--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_09_Waves.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_09_Waves.xlsx
@@ -1168,11 +1168,6 @@
           <t>একমাত্রিক তরঙ্গ সমীকরণ $\frac{\partial^2 y}{\partial t^2} = v^2 \frac{\partial^2 y}{\partial x^2}$ মেনে চলা একটি তরঙ্গের সমীকরণ $y(x, t) = A \sin(kx - \omega t)$। দেখাও যে মাধ্যমের কোনো বিন্দুর কণার বেগ $v_p = -v \left(\frac{\partial y}{\partial x}\right)$ এবং কণার ত্বরণ $a_p = - \omega^2 y$। তরঙ্গ বেগ এবং কণার বেগের মধ্যে মৌলিক ভৌত পার্থক্য বিশ্লেষণ করো।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>কণার বেগ ও তরঙ্গ বেগের অন্তরক সম্পর্ক:</t>
@@ -1218,11 +1213,6 @@
           <t>একটি তরঙ্গমুখের সমীকরণ $y(x, t) = \frac{0.05}{2 + (2x - 5t)^2}\text{ m}$। সমীকরণটি একটি বাস্তব তরঙ্গ নির্দেশ করে কি না যাচাই করো। তরঙ্গটির গতিবেগ, বিস্তার এবং গতির অভিমুখ নির্ণয় করো। $t = 1\text{ s}$ এবং $t = 2\text{ s}$ সময়ে তরঙ্গের শীর্ষবিন্দু (peak) কোন অবস্থানে অবস্থান করবে?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>তরঙ্গ ফাংশন $f(ax \pm bt)$-এর বিশ্লেষণ ও শীর্ষবিন্দুর ট্র্যাকিং:</t>
@@ -1268,11 +1258,6 @@
           <t>একটি টানা তারে অনুপ্রস্থ প্রগামী তরঙ্গের সমীকরণ $y(x, t) = 0.02 \sin(4\pi x - 100\pi t)$ [যেখানে $x, y$ মিটারে এবং $t$ সেকেন্ডে]। তারটির একক দৈর্ঘ্যের ভর $\mu = 0.05\text{ kg m}^{-1}$। (i) তারটিতে সঞ্চালিত গড় ক্ষমতা (average power $\langle P \rangle$) এবং (ii) একক দৈর্ঘ্যে সঞ্চিত মোট শক্তির গড় মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>অনুপ্রস্থ তরঙ্গে শক্তি প্রবাহ ও ক্ষমতা প্রতিপাদন:</t>
@@ -1318,11 +1303,6 @@
           <t>প্রগামী তরঙ্গে কণার তাৎক্ষণিক গতিশক্তি ঘনত্ব $u_k = \frac{1}{2}\mu \left(\frac{\partial y}{\partial t}\right)^2$ এবং স্থিতিস্থাপক স্থিতিশক্তি ঘনত্ব $u_p = \frac{1}{2}T \left(\frac{\partial y}{\partial x}\right)^2$। প্রমাণ করো যে প্রগামী তরঙ্গের যেকোনো বিন্দুতে যেকোনো মুহূর্তে $u_k = u_p$ এবং মোট তাৎক্ষণিক শক্তি ঘনত্ব $u(x, t) = \mu \omega^2 A^2 \cos^2(kx - \omega t)$। স্থির তরঙ্গের সাথে এই শক্তি বণ্টনের মূল পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>প্রগামী তরঙ্গে তাৎক্ষণিক শক্তি ঘনত্বের সমতা প্রমাণ:</t>
@@ -1368,11 +1348,6 @@
           <t>দুটি ভিন্ন উপাদানের তারকে একটি বিন্দুতে জোড়া লাগানো হয়েছে। প্রথম তারের একক দৈর্ঘ্যের ভর $\mu_1$ এবং দ্বিতীয় তারের $\mu_2$। একটি আপতিত অনুপ্রস্থ সাইনোসয়ডাল তরঙ্গ প্রথম তার বেয়ে সংযোগবিন্দুতে আপতিত হয়। সীমানা শর্ত ব্যবহার করে প্রতিফলিত তরঙ্গের বিস্তার $A_r$ এবং প্রতিসরিত তরঙ্গের বিস্তার $A_t$-এর সাথে আপতিত বিস্তার $A_i$-এর সম্পর্ক প্রতিপাদন করো। $\mu_2 \to \infty$ হলে কী ঘটে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>সংযোগবিন্দুতে তরঙ্গের প্রতিফলন ও সঞ্চালন গুণাঙ্ক প্রতিপাদন:</t>
@@ -1418,11 +1393,6 @@
           <t>প্রশ্ন ৫-এর সংযোগবিন্দুতে শক্তির সংরক্ষণ নীতি যাচাই করো। দেখাও যে আপতিত গড় ক্ষমতা, প্রতিফলিত গড় ক্ষমতা ও সঞ্চারিত গড় ক্ষমতার যোগফলের নিখুঁত সমান ($P_i = P_r + P_t$)।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>সীমানায় প্রতিফলন ও প্রতিসরণে শক্তির নিত্যতা প্রমাণ:</t>
@@ -1468,11 +1438,6 @@
           <t>একটি সাইন তরঙ্গ $y_1 = A \sin(kx - \omega t)$ একটি মুক্ত সীমানা ($x = 0$) থেকে প্রতিফলিত হয়, যেখানে কোনো উল্লম্ব বল নেই ($\partial y / \partial x = 0$)। প্রতিফলিত তরঙ্গের সমীকরণ এবং লব্ধি তরঙ্গের রূপ নির্ণয় করো। প্রতিফলনে কোনো দশা পরিবর্তন হয় কি?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>মুক্ত প্রান্তে তরঙ্গের প্রতিফলন ও দশা বিশ্লেষণ:</t>
@@ -1518,11 +1483,6 @@
           <t>একটি ত্রিকোণাকার স্পন্দন (triangular pulse) $t = 0$ মুহূর্তে শীর্ষবিন্দু $(x = 0, y = h)$ এবং ভিত্তি $x = -b$ থেকে $x = +b$ পর্যন্ত বিস্তৃত। স্পন্দনটি $v$ দ্রুতিতে ধনাত্মক $x$-অক্ষে গতিশীল। যেকোনো সময় $t$-এর জন্য কণার বেগ বন্টন $v_p(x)$ লেখচিত্রের প্রকৃতি বিশ্লেষণ করো।</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>নন-সাইনোসয়ডাল স্পন্দনে কণার বেগ বিশ্লেষণ:</t>
@@ -1619,11 +1579,6 @@
           <t>মাধ্যমের বিচ্ছুরণ (dispersion) ধর্ম থাকলে তরঙ্গের দশা বেগ (phase velocity $v_p = \omega/k$) এবং দলগত বেগ (group velocity $v_g = d\omega/dk$)-এর মধ্যে পার্থক্য দেখা দেয়। দেখাও যে $v_g = v_p - \lambda \frac{dv_p}{d\lambda}$। একটি গভীর পানির মহাকর্ষীয় তরঙ্গে যদি $\omega = \sqrt{gk}$ হয়, তবে $v_g$ এবং $v_p$-এর অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>বিচ্ছুরণ মাধ্যমে ফেজ বেগ ও গ্রুপ বেগের সম্পর্ক প্রতিপাদন:</t>
@@ -1669,11 +1624,6 @@
           <t>সুষম উপাদান ও সুষম প্রস্থচ্ছেদের $M$ ভরের এবং $L$ দৈর্ঘ্যের একটি ভারী দড়ি ছাদ থেকে উলম্বভাবে ঝুলছে। দড়ির নিম্ন প্রান্ত থেকে $x$ উচ্চতায় অনুপ্রস্থ তরঙ্গের গতিবেগ $v(x) = \sqrt{gx}$ প্রতিপাদন করো। নিম্ন প্রান্তে একটি অনুপ্রস্থ কম্পন সৃষ্টি করলে সেই স্পন্দনটি ছাদ পর্যন্ত পৌঁছাতে কত সময় লাগবে?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>নিজস্ব ওজনে ঝুলন্ত ভারী দড়িতে তরঙ্গের বেগ ও আরোহণকাল:</t>
@@ -1719,11 +1669,6 @@
           <t>প্রশ্ন ১১-এর ঝুলন্ত দড়ির নিম্ন প্রান্তে $m$ ভরের একটি অতিরিক্ত বস্তু ঝুলিয়ে দেওয়া হলো। এবার নিম্ন প্রান্ত থেকে সৃষ্ট তরঙ্গের ছাদ পর্যন্ত পৌঁছাতে প্রয়োজনীয় সময়ের রাশিমালা প্রতিপাদন করো। $m \gg M$ হলে ফলাফলটি কীভাবে ধ্রুব টানের সূত্রের সাথে মিলে যায় দেখাও।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>ভারযুক্ত ভারী দড়িতে তরঙ্গ সঞ্চালনের সামগ্রিক সময়কাল:</t>
@@ -1769,11 +1714,6 @@
           <t>উল্লম্বভাবে ঝুলন্ত ভারী দড়ির নিম্ন প্রান্তে একটি উৎস দ্বারা ধ্রুব কম্পাঙ্ক $f$-এর তরঙ্গ অবিরাম সৃষ্টি করা হচ্ছে। দেখাও যে নিম্ন প্রান্ত থেকে $x$ উচ্চতায় তরঙ্গের তরঙ্গদৈর্ঘ্য $\lambda(x) \propto \sqrt{x}$। দড়ির শীর্ষ প্রান্তে তরঙ্গদৈর্ঘ্য নিম্ন প্রান্তের নিকটবর্তী কোনো বিন্দুর চেয়ে বেশি হয় কেন?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>পরিবর্তনশীল টানে তরঙ্গদৈর্ঘ্যের উচ্চতানির্ভরতা বিশ্লেষণ:</t>
@@ -1819,11 +1759,6 @@
           <t>$L$ দৈর্ঘ্যের এবং $M$ ভরের একটি সুষম দড়ি ছাদ থেকে ঝুলছে। একটি কণা একই মুহূর্তে দড়ির শীর্ষবিন্দু থেকে মুক্তভাবে নিচে পড়তে শুরু করে এবং দড়ির নিম্ন প্রান্ত থেকে একটি অনুপ্রস্থ তরঙ্গ শীর্ষবিন্দুর উদ্দেশ্যে যাত্রা করে। তারা দড়ির শীর্ষবিন্দু থেকে কত দূরত্বে মিলিত হবে?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>মুক্ত পতনশীল কণা ও আরোহণকারী তরঙ্গের সাক্ষাৎ বিন্দু নির্ণয়:</t>
@@ -1869,11 +1804,6 @@
           <t>$R$ ব্যাসার্ধ এবং $\mu$ রৈখিক ভরের একটি সুষম নমনীয় বৃত্তাকার রিং তার কেন্দ্রের মধ্যগামী লম্ব অক্ষের সাপেক্ষে মহাকাশে ধ্রুব কৌণিক বেগ $\omega$-তে আবর্তিত হচ্ছে। রিংয়ের মধ্যে ঘূর্ণনজনিত সেন্ট্রিফিউগাল বলের কারণে উদ্ভূত টান $T = \mu \omega^2 R^2$ প্রতিপাদন করো। রিংয়ের ওপর একটি অনুপ্রস্থ স্পন্দন সৃষ্টি করলে স্থির দর্শকের সাপেক্ষে স্পন্দনটির গতিবেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>ঘূর্ণায়মান রিংয়ে অনুপ্রস্থ তরঙ্গের বেগ ও আপেক্ষিক গতি:</t>
@@ -1919,11 +1849,6 @@
           <t>একটি লিফট $a$ সুষম ঊর্ধ্বমুখী ত্বরণে উঠছে। লিফটের ছাদ থেকে $L$ দৈর্ঘ্যের এবং $M$ ভরের একটি সুষম দড়ি ঝুলানো আছে। নিম্ন প্রান্তে সৃষ্ট একটি অনুপ্রস্থ তরঙ্গ ছাদ পর্যন্ত পৌঁছাতে কত সময় নেবে? লিফটের তার ছিঁড়ে মুক্ত পতনের সময় দড়িতে কোনো অনুপ্রস্থ তরঙ্গ সঞ্চালিত হতে পারবে কি?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>ত্বরিত ফ্রেমে টানাতারের তরঙ্গ বেগ ও ভারহীনতার প্রভাব:</t>
@@ -1969,11 +1894,6 @@
           <t>একটি শঙ্কু আকৃতির (conical tapering) ভারী দড়ির রৈখিক ভর ঘনত্ব দৈর্ঘ্যের সাথে রৈখিকভাবে বৃদ্ধি পায়: $\mu(x) = \mu_0 \left(1 + \frac{x}{L}\right)$, যেখানে $x = 0$ থেকে $x = L$। দড়িটিতে ধ্রুব টান $T_0$ বজায় রাখা আছে। তরঙ্গটি এক প্রান্ত থেকে অপর প্রান্তে পৌঁছাতে প্রয়োজনীয় সময় নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>পরিবর্তনশীল রৈখিক ঘনত্বের তারে তরঙ্গের সময় সমাকলন:</t>
@@ -2019,11 +1939,6 @@
           <t>একটি টানাতারে অনুপ্রস্থ তরঙ্গের চলাচলের সময় তারটির উপাদান স্থিতিস্থাপকভাবে প্রসারিত হয়। দেখাও যে তারের আপেক্ষিক দৈর্ঘ্য বৃদ্ধি $\frac{\Delta l}{dx} \approx \frac{1}{2}\left(\frac{\partial y}{\partial x}\right)^2$ এবং এই অতিরিক্ত স্থিতিস্থাপক প্রসারণের জন্য তারের স্থিতিশক্তি ঘনত্ব $\frac{1}{2}T \left(\frac{\partial y}{\partial x}\right)^2$ রূপ ধারণ করে।</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>জ্যামিতিক বিকৃতি ও স্থিতিস্থাপক স্থিতিশক্তির আন্তঃসম্পর্ক:</t>
@@ -2069,11 +1984,6 @@
           <t>একটি টানাতারে বিপরীত দিক থেকে দুটি অভিন্ন আয়তাকার স্পন্দন (rectangular pulse) সমান বেগে পরস্পরের দিকে অগ্রসর হচ্ছে। যখন তারা একে অপরকে সম্পূর্ণ সমাপতিত (overlap) করে, তখন এক মুহূর্তে তারটি সম্পূর্ণ সরলরেখায় সোজা হয়ে যায় ($y(x) = 0$)। ওই তাৎক্ষণিক মুহূর্তে তরঙ্গের সমুদয় যান্ত্রিক শক্তি কোথায় অবস্থান করে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>সম্পূর্ণ উপরিপাতন মুহূর্তে শক্তির রূপান্তর বিশ্লেষণ:</t>
@@ -2119,11 +2029,6 @@
           <t>ভারী ঝুলন্ত দড়িতে নিচ থেকে উপরে ওঠার সময় তরঙ্গের বিস্তার $A(x)$-এর পরিবর্তন বিশ্লেষণ করো। শক্তির নিত্যতা বিবেচনা করে প্রমাণ করো যে বিস্তার উচ্চতার সাথে $A(x) \propto x^{-1/4}$ অনুসারে হ্রাস পায়। কেন শীর্ষের কাছাকাছি তরঙ্গের বিস্তার অত্যন্ত ক্ষুদ্র হয়?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>পরিবর্তনশীল টানে তরঙ্গের বিস্তার ক্ষয়ের শক্তি সংরক্ষণ সূত্র:</t>
@@ -2169,11 +2074,6 @@
           <t>উভয় প্রান্তে আবদ্ধ $L$ দৈর্ঘ্যের একটি তারের স্বাভাবিক মোডসমূহের (normal modes) গতির সমীকরণ $y_n(x, t) = 2A \sin\left(\frac{n\pi x}{L}\right)\cos(\omega_n t)$। প্রমাণ করো যে যেকোনো দুটি ভিন্ন মোডের ($n \neq m$) স্থানিক তরঙ্গ ফাংশন পরস্পরের সাপেক্ষে লম্ব (orthogonality condition), অর্থাৎ $\int_0^L \sin\left(\frac{n\pi x}{L}\right)\sin\left(\frac{m\pi x}{L}\right)dx = 0$। ফুরিয়ার বিশ্লেষণে এর তাৎপর্য কী?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>স্বাভাবিক মোডসমূহের লম্বতা উপপাদ্য প্রমাণ:</t>
@@ -2219,11 +2119,6 @@
           <t>উভয় প্রান্তে আটকানো একটি টানাতারের দৈর্ঘ্য $L$ এবং টান $T$। তারটিকে মধ্যবিন্দু $x = L/2$-তে টেনে $h$ উচ্চতায় তুলে স্থির অবস্থা থেকে ছেড়ে দেওয়া হলো। ফুরিয়ার সহগ নির্ণয় করে দেখাও যে গতিতে কেবল বিজোড় হারমোনিকসমূহ ($n = 1, 3, 5, \dots$) উপস্থিত থাকে এবং কেন সকল জোড় হারমোনিক সম্পূর্ণ অনুপস্থিত থাকে?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>ত্রিকোণাকার প্রাথমিক সরণের ফুরিয়ার হারমোনিক বিশ্লেষণ:</t>
@@ -2269,11 +2164,6 @@
           <t>মেলডির পরীক্ষায় (Melde's experiment) একটি টিউনিং ফর্ক দিয়ে তারে স্থির তরঙ্গ সৃষ্টি করা হয়। (i) অনুপ্রস্থ বিন্যাসে (transverse arrangement) ফর্কের কম্পাঙ্ক $f_F$ এবং তারের কম্পাঙ্ক $f_w$-এর অনুপাত কত? (ii) অনুদৈর্ঘ্য বিন্যাসে (longitudinal arrangement) এই অনুপাত কত এবং কেন অনুদৈর্ঘ্য বিন্যাসে তারের কম্পাঙ্ক ফর্কের কম্পাঙ্কের অর্ধেক হয়?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>মেলডির পরীক্ষায় অনুপ্রস্থ ও অনুদৈর্ঘ্য বিন্যাসের কম্পাঙ্ক অনুপাত:</t>
@@ -2319,11 +2209,6 @@
           <t>সোনোমিটারের একটি স্টিলের তারের দুই প্রান্ত দুটি অনড় অবলম্বনে আটকানো আছে। তাপমাত্রা $\Delta \theta = 20^\circ\text{C}$ হ্রাস পেলে তারটির মূল সুরের কম্পাঙ্ক কত শতাংশ বৃদ্ধি পাবে? স্টিলের ইয়ং-এর গুণাঙ্ক $Y = 2 \times 10^{11}\text{ N m}^{-2}$, ঘনত্ব $\rho = 7800\text{ kg m}^{-3}$, এবং রৈখিক প্রসারণ সহগ $\alpha = 1.2 \times 10^{-5}\text{ K}^{-1}$। আদি টান বল $T_0 = 100\text{ N}$ এবং তারের ব্যাসার্ধ $r = 0.5\text{ mm}$।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>তাপীয় পীড়ন জনিত সোনোমিটার তারের কম্পাঙ্ক পরিবর্তন:</t>
@@ -2420,11 +2305,6 @@
           <t>$L$ দৈর্ঘ্যের একটি তারের রৈখিক ভর ঘনত্ব সুষম নয় এবং তা $\mu(x) = \mu_0 \left(1 + \frac{x}{L}\right)$ সমীকরণ মেনে চলে। তারটিতে $T$ টান প্রয়োগ করা হয়েছে। ডাব্লিউকেবি (WKB) বা ফেজ ইন্টিগ্রাল পদ্ধতির সাহায্যে তারটির স্বাভাবিক কম্পন মোডসমূহের কম্পাঙ্ক $f_n$-এর আসন্ন রাশিমালা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>অসুষম টানাতারের WKB কোয়ান্টাইজেশন কম্পাঙ্ক প্রতিপাদন:</t>
@@ -2470,11 +2350,6 @@
           <t>একটি সংযুক্ত তারে (composite wire) $L_1$ দৈর্ঘ্যের ও $\mu_1$ ঘনত্বের একটি তারের সাথে $L_2$ দৈর্ঘ্যের ও $\mu_2$ ঘনত্বের অপর একটি তার জোড়া লাগানো। উভয় প্রান্ত দৃঢ়ভাবে আবদ্ধ এবং উভয় অংশে টান $T$ সমান। ব্যবস্থাটির স্বাভাবিক মোডের সাধারণ শর্ত $\tan(k_1 L_1)\tan(k_2 L_2) = \frac{k_1}{k_2} = \frac{v_2}{v_1} = \sqrt{\frac{\mu_1}{\mu_2}}$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>সংযুক্ত তারের স্থির তরঙ্গের বিচ্ছিন্নতা সমীকরণ প্রতিপাদন:</t>
@@ -2520,11 +2395,6 @@
           <t>স্থির তরঙ্গে পরপর দুটি নোডের মধ্যবর্তী সকল কণার দশা সম্পর্ক কেমন হয়? বিপরীত পাশের দুটি পাশাপাশি লুপের (adjacent loops) কণাগুলোর মধ্যবর্তী দশা পার্থক্য কত? স্থির তরঙ্গে কেন কোনো নেট শক্তি সঞ্চালিত হয় না তা গাণিতিকভাবে প্রমাণ করো।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>স্থির তরঙ্গের দশা বন্টন ও শূন্য শক্তি প্রবাহের প্রমাণ:</t>
@@ -2570,11 +2440,6 @@
           <t>সোনোমিটারের তারের ব্যাস $d$, টান $T$ এবং ঘনত্ব $\rho$। প্রমাণ করো যে তারটির মূল সুরের কম্পাঙ্ক $f = \frac{1}{L d}\sqrt{\frac{T}{\pi \rho}}$। যদি তারের ব্যাস $10\%$ বৃদ্ধি করা হয় এবং টান $21\%$ বৃদ্ধি করা হয়, তবে কম্পাঙ্কের শতকরা পরিবর্তন কত হবে?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>সোনোমিটারের পরামিতিক নির্ভরতা ও পরিবর্তনের হার নির্ণয়:</t>
@@ -2620,11 +2485,6 @@
           <t>একটি টানাতারে স্থির তরঙ্গ গঠিত হওয়ায় মোট শক্তি $E$ সঞ্চিত আছে। দেখাও যে যখন তারটি সম্পূর্ণ সমতল বা অনুভূমিক অবস্থায় আসে ($y(x) = 0$), তখন তারটিতে গতিশক্তি সর্বোচ্চ হয় এবং স্থিতিশক্তি শূন্য হয়। আবার যখন তারটি সর্বোচ্চ বক্রতা ধারণ করে, তখন গতিশক্তি শূন্য এবং স্থিতিশক্তি সম্পূর্ণ $E$-এর সমান হয়। সমাকলন দ্বারা এটি প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>স্থির তরঙ্গে গতিশক্তি ও স্থিতিশক্তির পর্যায়ক্রমিক বিনিময় প্রমাণ:</t>
@@ -2670,11 +2530,6 @@
           <t>শব্দ তরঙ্গের সঞ্চালনে নিউটনের সমোষ্ণ (isothermal) সূত্র $v = \sqrt{P/\rho}$ কেন ত্রুটিপূর্ণ ছিল এবং ল্যাপলাস কীভাবে রুদ্ধতাপীয় (adiabatic) সংশোধনের মাধ্যমে $v = \sqrt{\gamma P/\rho}$ প্রতিপাদন করেন? শব্দ সঞ্চালন প্রক্রিয়াটি সমোষ্ণ না হয়ে কেন রুদ্ধতাপীয় হয় তার ভৌত কারণ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>নিউটনের সূত্র বনাম ল্যাপলাসের রুদ্ধতাপীয় সংশোধন:</t>
@@ -2720,11 +2575,6 @@
           <t>অনুদৈর্ঘ্য শব্দ তরঙ্গে সরণ তরঙ্গ $s(x, t) = s_0 \cos(kx - \omega t)$ হলে অতিরিক্ত চাপ তরঙ্গের সমীকরণ $\Delta P(x, t) = \Delta P_0 \sin(kx - \omega t)$ প্রতিপাদন করো। দেখাও যে চাপ তরঙ্গের বিস্তার $\Delta P_0 = B k s_0 = \rho v \omega s_0$ এবং সরণ তরঙ্গ ও চাপ তরঙ্গের মধ্যে দশা পার্থক্য $90^\circ$ বা $\pi/2$।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>সরণ তরঙ্গ ও চাপ তরঙ্গের অন্তরক সম্পর্ক ও দশা পার্থক্য প্রতিপাদন:</t>
@@ -2770,11 +2620,6 @@
           <t>আদর্শ গ্যাসে শব্দের দ্রুতি $v = \sqrt{\frac{\gamma R T}{M}}$। দেখাও যে স্থির তাপমাত্রায় চাপ দ্বিগুণ বা চারগুণ করলে শব্দবেগের কোনো পরিবর্তন হয় না। প্রমাণ করো যে সেলসিয়াস স্কেলে ক্ষুদ্র তাপমাত্রার জন্য শব্দবেগ $v_t \approx v_0 + 0.61 t\text{ m s}^{-1}$।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>শব্দবেগের চাপ নিরপেক্ষতা ও তাপমাত্রা নির্ভরতা প্রতিপাদন:</t>
@@ -2820,11 +2665,6 @@
           <t>শুষ্ক বাতাসের তুলনায় আর্দ্র বাতাসে শব্দের বেগ বেশি হয় কেন? প্রমাণ বায়ুমণ্ডলীয় চাপ ও $27^\circ\text{C}$ তাপমাত্রায় আপেক্ষিক আর্দ্রতা বৃদ্ধি পেলে বাতাসে শব্দবেগ বৃদ্ধির হার আণবিক ভরের পরিবর্তনের সাহায্যে গাণিতিকভাবে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>আর্দ্র বাতাসে আণবিক ভর হ্রাস ও শব্দবেগ বৃদ্ধি বিশ্লেষণ:</t>
@@ -2870,11 +2710,6 @@
           <t>একটি গ্যাস মিশ্রণে $1\text{ mol}$ হিলিয়াম ($\text{He}$, $\gamma_1 = 5/3$) এবং $2\text{ mol}$ নাইট্রোজেন ($\text{N}_2$, $\gamma_2 = 7/5$) মিশ্রিত আছে। $300\text{ K}$ তাপমাত্রায় এই মিশ্রণে শব্দের বেগ কত? [$R = 8.314\text{ J mol}^{-1}\text{ K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>গ্যাস মিশ্রণে কার্যকর গামা, আণবিক ভর ও শব্দবেগ নির্ণয়:</t>
@@ -2920,11 +2755,6 @@
           <t>শব্দ তরঙ্গের তীব্রতা $I = \frac{\Delta P_0^2}{2\rho v}$ প্রতিপাদন করো। প্রমাণ করো যে তীব্রতাকে কণার সরণ বিস্তারের মাধ্যমে লিখলে $I = \frac{1}{2}\rho v \omega^2 s_0^2$ হয়। বাতাসে $1000\text{ Hz}$ কম্পাঙ্কের একটি শব্দের তীব্রতা $I = 10^{-6}\text{ W m}^{-2}$ হলে বাতাসের কণাগুলোর সরণ বিস্তার $s_0$ এবং চাপ বিস্তার $\Delta P_0$ কত? [বাতাসের $\rho = 1.2\text{ kg m}^{-3}$, $v = 340\text{ m s}^{-1}$]</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>শব্দ তরঙ্গের তীব্রতা, চাপ বিস্তার ও সরণ বিস্তারের আন্তঃসম্পর্ক:</t>
@@ -2970,11 +2800,6 @@
           <t>নির্দিষ্ট শাব্দিক প্রতিবন্ধকতা (specific acoustic impedance) $Z = \rho v$ বলতে কী বোঝায়? দুটি বায়বীয় মাধ্যমের সংযোগস্থলে লম্বভাবে আপতিত শব্দের জন্য প্রতিফলন সহগ $R_p = \frac{Z_2 - Z_1}{Z_2 + Z_1}$ এবং সঞ্চালন সহগ $T_p = \frac{2Z_2}{Z_2 + Z_1}$ চাপ বিস্তারের নিরিখে প্রতিপাদন করো। বায়ু ও পানির সংযোগস্থলে প্রায় $99.9\%$ শব্দ প্রতিফলিত হওয়ার কারণ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>শব্দ তরঙ্গের একোস্টিক ইম্পিডেন্স ও বায়ু-পানি ইন্টারফেসে প্রতিফলন:</t>
@@ -3020,11 +2845,6 @@
           <t>একটি দীর্ঘ কঠিন ইস্পাত রডে অনুদৈর্ঘ্য তরঙ্গের বেগ $v = \sqrt{Y/\rho}$। যদি রডের দৈর্ঘ্য $L = 2\text{ m}$, ঘনত্ব $\rho = 7800\text{ kg m}^{-3}$ এবং ইয়ং-এর গুণাঙ্ক $Y = 2 \times 10^{11}\text{ N m}^{-2}$ হয়, তবে রডটির মধ্যবিন্দুতে আটকে দুই প্রান্ত মুক্ত অবস্থায় রাখলে এর মৌলিক অনুদৈর্ঘ্য কম্পাঙ্ক কত হবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>ধাতব রডে অনুদৈর্ঘ্য কম্পন ও কুন্ডটের পরীক্ষা নীতি:</t>
@@ -3070,11 +2890,6 @@
           <t>একটি সুপারসনিক জেট বিমান অনুভূমিকভাবে শব্দের দ্রুতির $2$ গুণ বেগে ($M = 2$, Mach 2) উড়ে যাচ্ছে। জেট বিমানটির পেছনে সৃষ্ট ম্যাক শঙ্কুর অর্ধ-শীর্ষ কোণ (Mach cone half-angle $\theta_M$) কত? বিমানটি একজন দর্শকের ঠিক মাথার ওপর দিয়ে চলে যাওয়ার কত সময় পর দর্শকটি সনিক বুম (sonic boom) শুনতে পাবেন, যদি বিমানটি $h = 3400\text{ m}$ উচ্চতায় উড়তে থাকে? [$v_{\text{sound}} = 340\text{ m s}^{-1}$]</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>ম্যাক শঙ্কু ও সনিক বুম বিলম্ব কাল গণনা:</t>
@@ -3120,11 +2935,6 @@
           <t>গ্যাসে অনুদৈর্ঘ্য তরঙ্গের ক্ষেত্রে আয়তন বিকৃতি ও অতিরিক্ত চাপের সম্পর্ক আলোচনা করো। প্রমাণ করো যে একটি তরঙ্গের সর্বোচ্চ চাপের বিন্দুগুলো সর্বোচ্চ ঘনত্বের সাথে মিলে যায় এবং সর্বনিম্ন চাপের বিন্দুগুলো সর্বনিম্ন ঘনত্বের সাথে মিলে যায়। চাপের আপেক্ষিক পরিবর্তন $\frac{\Delta P}{P_0}$ এবং ঘনত্বের আপেক্ষিক পরিবর্তন $\frac{\Delta \rho}{\rho_0}$-এর সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>চাপ ও ঘনত্বের ওঠানামার রুদ্ধতাপীয় সম্পর্ক:</t>
@@ -3170,11 +2980,6 @@
           <t>উভয় মুখ খোলা অর্গান পাইপ (open pipe) এবং এক মুখ বন্ধ অর্গান পাইপের (closed pipe) বিভিন্ন হারমোনিকের কম্পাঙ্কের অনুপাত প্রতিপাদন করো। সুরের গুণগত মানের (timbre বা musical quality) বিচারে খোলা পাইপের ধ্বনি কেন বন্ধ পাইপের চেয়ে অনেক বেশি শ্রুতিমধুর ও সমৃদ্ধ?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>খোলা ও বন্ধ পাইপের হারমোনিক অনুপাত ও সুরের সমৃদ্ধি তুলনা:</t>
@@ -3220,11 +3025,6 @@
           <t>লর্ড র্যালের (Lord Rayleigh) প্রান্ত সংশোধন (end correction $e$) নীতি কী? পাইপের খোলা মুখের ব্যাসার্ধ $r$ হলে প্রমাণ করো যে খোলা পাইপের ক্ষেত্রে কার্যকর দৈর্ঘ্য $L_{\text{eff}} = L + 2e \approx L + 1.2 r$ এবং বন্ধ পাইপের ক্ষেত্রে $L_{\text{eff}} = L + e \approx L + 0.6 r$। খোলা মুখেই সরণ অ্যান্টিনোড নিখুঁতভাবে গঠিত না হয়ে সামান্য বাইরে গঠিত হয় কেন?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>প্রান্ত সংশোধনের ভৌত কারণ ও কার্যকর দৈর্ঘ্য সমীকরণ:</t>
@@ -3270,11 +3070,6 @@
           <t>একটি রেজোন্যান্স টিউব পরীক্ষায় $f = 512\text{ Hz}$ কম্পাঙ্কের সুরশলাকা ব্যবহার করা হলো। প্রথম ও দ্বিতীয় অনুনাদের সময় পানির পৃষ্ঠের পাঠ যথাক্রমে $l_1 = 15.8\text{ cm}$ এবং $l_2 = 49.2\text{ cm}$ পাওয়া গেল। প্রান্ত সংশোধন বাদ না দিয়ে বাতাসে শব্দের গতিবেগ এবং টিউবটির প্রান্ত সংশোধন ও অন্তঃব্যাস নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>রেজোন্যান্স টিউব থেকে শব্দবেগ ও প্রান্ত সংশোধন গণনা:</t>
@@ -3320,11 +3115,6 @@
           <t>একটি বন্ধ অর্গান পাইপের মৌলিক কম্পাঙ্ক একটি খোলা অর্গান পাইপের দ্বিতীয় ওভারটোনের (third harmonic) কম্পাঙ্কের সমান। বন্ধ পাইপের দৈর্ঘ্য $L_c$ এবং খোলা পাইপের দৈর্ঘ্য $L_o$-এর অনুপাত নির্ণয় করো (প্রান্ত সংশোধন উপেক্ষা করো)।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>বন্ধ পাইপের মূল সুর বনাম খোলা পাইপের হারমোনিক তুলনা:</t>
@@ -3370,11 +3160,6 @@
           <t>গ্রীষ্মকালে তাপমাত্রা $35^\circ\text{C}$ এবং শীতকালে তাপমাত্রা $15^\circ\text{C}$। একটি অর্গান পাইপের মৌলিক কম্পাঙ্ক শীতকালের তুলনায় গ্রীষ্মকালে শতকরা কত পরিবর্তিত হবে? পাইপের উপাদানের তাপীয় প্রসারণ উপেক্ষণীয় বিবেচনা করো। তাপমাত্রা বাড়লে অর্গান পাইপের সুর চড়া (sharp) হয় না খাদে (flat) নামে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>তাপমাত্রা পরিবর্তনে অর্গান পাইপের ফ্রিকোয়েন্সি শিফট:</t>
@@ -3420,11 +3205,6 @@
           <t>একটি খোলা অর্গান পাইপ স্বাভাবিক অবস্থায় বাতাসে বাজানো হচ্ছে। এরপর পাইপটিকে হিলিয়াম গ্যাসপূর্ণ ($\text{He}$, $M = 4\text{ g mol}^{-1}$, $\gamma = 5/3$) একটি প্রকোষ্ঠে নেওয়া হলো। পাইপটির মূল সুরের কম্পাঙ্ক স্বাভাবিক বাতাসের ($M = 28.97\text{ g mol}^{-1}$, $\gamma = 1.4$) তুলনায় কত গুণ বৃদ্ধি পাবে? [তাপমাত্রা উভয় ক্ষেত্রে সমান]</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>গ্যাস পরিবর্তনের ফলে অর্গান পাইপের কম্পাঙ্ক বৃদ্ধি:</t>
@@ -3470,11 +3250,6 @@
           <t>একটি $L$ দৈর্ঘ্যের খোলা অর্গান পাইপ তার মূল সুরে কম্পিত হচ্ছে। পাইপটির অর্ধেকাংশ ($L/2$) হঠাৎ পানিতে ডুবিয়ে বন্ধ পাইপে রূপান্তর করা হলো। নতুন অবস্থায় উৎপন্ন মূল সুরের কম্পাঙ্ক পূর্বের মূল সুরের কম্পাঙ্কের সাথে কীভাবে সম্পর্কিত হবে?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>দৈর্ঘ্য হ্রাস ও বন্ধ পাইপে রূপান্তরের যৌথ প্রভাব:</t>
@@ -3520,11 +3295,6 @@
           <t>কুন্ডটের নলে (Kundt's tube) একটি ধাতব রডের অনুদৈর্ঘ্য কম্পন দ্বারা কাঁচের নলের ভেতরে থাকা লাইকোপোডিয়াম পাউডারের স্তূপে স্থির তরঙ্গের প্যাটার্ন তৈরি করা হয়। নলে পরপর দুটি পাউডারের স্তূপের মধ্যবর্তী দূরত্ব $d$ এবং রডের দৈর্ঘ্য $L_r$। রডে শব্দের বেগ এবং বাতাসে শব্দের বেগের অনুপাত নির্ণয়ের সূত্র প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>কুন্ডটের নলে শব্দবেগ ও স্থিতিস্থাপক গুণাঙ্ক নির্ণয়ের সমীকরণ:</t>
@@ -3570,11 +3340,6 @@
           <t>একটি শঙ্কু আকৃতির অর্গান পাইপ (conical organ pipe) যার শীর্ষবিন্দু বন্ধ এবং তলদেশ খোলা, তার দৈর্ঘ্য $L$। গোলকীয় প্রতিসাম্যের তরঙ্গ সমীকরণ $\frac{\partial^2(r \psi)}{\partial t^2} = v^2 \frac{\partial^2(r \psi)}{\partial r^2}$ ব্যবহার করে দেখাও যে এর হারমোনিক কম্পাঙ্কসমূহ খোলা সিলিন্ডার আকৃতির পাইপের মতো সকল জোড় ও বিজোড় পূর্ণসংখ্যার গুণিতক হয় ($f_n = n \frac{v}{2L}$)।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>শঙ্কু আকৃতির অর্গান পাইপের স্বাভাবিক মোড বিশ্লেষণ:</t>
@@ -3655,7 +3420,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ (সমস্যা 1)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3664,34 +3429,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ]
-##PRESET:wave-transverse[size:medium]##
-একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.04 \sin(200\pi t - 3\pi x)\text{ m}$। তরঙ্গটির বিস্তার, কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের বেগ কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.05\sin(200\pi t - 4\pi x)$ মিটার, যেখানে $x$ ও $y$ মিটারে এবং $t$ সেকেন্ডে। তরঙ্গটির কম্পাঙ্ক $f$, তরঙ্গদৈর্ঘ্য $\lambda$, তরঙ্গবেগ $v$ এবং কণার সর্বোচ্চ বেগ $v_{p,\max}$ ও ত্বরণ $a_{p,\max}$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:wave-transverse[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 1)।</t>
+          <t>সমীকরণ $y = A\sin(\omega t - kx)$ এর সাথে তুলনা করে: বিস্তার $A = 0.05\text{ m}$, কৌণিক কম্পাঙ্ক $\omega = 200\pi\text{ rad/s} \implies f = \frac{200\pi}{2\pi} = 100\text{ Hz}$। তরঙ্গ সংখ্যা $k = 4\pi\text{ rad/m} \implies \lambda = \frac{2\pi}{k} = \frac{2\pi}{4\pi} = 0.5\text{ m}$। তরঙ্গবেগ $v = f\lambda = 100 \times 0.5 = 50\text{ m/s}$। কণার সর্বোচ্চ বেগ $v_{p,\max} = \omega A = 200\pi(0.05) = 10\pi \approx 31.42\text{ m/s}$। কণার সর্বোচ্চ ত্বরণ $a_{p,\max} = \omega^2 A = (200\pi)^2(0.05) = 2000\pi^2 \approx 19739.2\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>$f = 100\text{ Hz}, \lambda = 0.5\text{ m}, v = 50\text{ m/s}, v_{p,\max} = 10\pi\text{ m/s} \approx 31.42\text{ m/s}, a_{p,\max} = 2000\pi^2\text{ m/s}^2 \approx 19739.2\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3711,12 +3471,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ডপলার ক্রিয়া ও চলমান ট্রেন (সমস্যা 2)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3724,30 +3484,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: ডপলার ক্রিয়া ও চলমান ট্রেন]
-##PRESET:doppler-effect[size:medium]##
-একটি ট্রেনের সাইরেন $f = 600\text{ Hz}$ শব্দ করে $v_s = 50\text{ m/s}$ বেগে প্ল্যাটফর্মের দিকে এগিয়ে আসছে। প্ল্যাটফর্মে দাঁড়ানো একজন শ্রোতার কাছে শব্দের আপাত কম্পাঙ্ক কত মনে হবে? ($v = 340\text{ m/s}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি চলমান তরঙ্গে দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 15\text{ cm}$ এবং এদের মধ্যকার দশা পার্থক্য $\Delta\phi = \frac{3\pi}{4}\text{ rad}$। তরঙ্গটির তরঙ্গদৈর্ঘ্য $\lambda$ কত? যদি তরঙ্গের কম্পাঙ্ক $400\text{ Hz}$ হয়, তবে মাধ্যমের তরঙ্গবেগ কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:doppler-effect[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 2)।</t>
+          <t>দশা পার্থক্য ও পথ পার্থক্যের সম্পর্ক: $\Delta\phi = \frac{2\pi}{\lambda}\Delta x \implies \frac{3\pi}{4} = \frac{2\pi}{\lambda}(15) \implies \lambda = \frac{2\pi \times 15}{3\pi/4} = \frac{30 \times 4}{3} = 40.0\text{ cm} = 0.40\text{ m}$। তরঙ্গবেগ $v = f\lambda = 400 \times 0.40 = 160.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>$\lambda = 40.0\text{ cm} = 0.40\text{ m}$, $v = 160.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3767,7 +3522,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>টান টান তারে স্থির তরঙ্গ (সমস্যা 3)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3776,29 +3531,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: টান টান তারে স্থির তরঙ্গ]
-$L = 1.0\text{ m}$ দীর্ঘ এবং $m = 8\text{ g}$ ভরের একটি তারে $T = 700\text{ N}$ টান প্রযুক্ত রয়েছে। তারটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক ($f_1 = \frac{1}{2L}\sqrt{\frac{T}{\mu}}$) কত?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1][size:small]##
+একটি অনুভূমিক তারের একক দৈর্ঘ্যের ভর $\mu = 5.0 	imes 10^{-3}\text{ kg/m}$। তারটিতে $T = 180\text{ N}$ টান প্রযুক্ত হলে অনুপ্রস্থ তরঙ্গের বেগ কত? তরঙ্গের কম্পাঙ্ক $120\text{ Hz}$ হলে তরঙ্গদৈর্ঘ্য কত?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 3)।</t>
+          <t>তারের অনুপ্রস্থ তরঙ্গের বেগ $v = \sqrt{\frac{T}{\mu}} = \sqrt{\frac{180}{5.0 \times 10^{-3}}} = \sqrt{36000} \approx 189.74\text{ m/s}$। তরঙ্গদৈর্ঘ্য $\lambda = \frac{v}{f} = \frac{189.74}{120} \approx 1.581\text{ m}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>বেগ $v = 189.74\text{ m/s}$, $\lambda = 1.58\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3818,12 +3573,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>বিট বা স্বরকম্প গণনা (সমস্যা 4)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3831,25 +3586,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: বিট বা স্বরকম্প গণনা]
-দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে 10টি বিট শোনা যায়। $A$-এর কম্পাঙ্ক $900\text{ Hz}$। $B$-তে কিছুটা মোম লাগালে বিট সংখ্যা বৃদ্ধি পেয়ে 6টি হয়। $B$-এর প্রকৃত কম্পাঙ্ক কত?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বায়ুতে $0^\circ\text{C}$ তাপমাত্রায় শব্দের বেগ $332\text{ m/s}$। কত তাপমাত্রায় শব্দের বেগ $0^\circ\text{C}$ তাপমাত্রার বেগের $1.5$ গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 4)।</t>
+          <t>শব্দের বেগ $v \propto \sqrt{T}$। $\frac{v_2}{v_1} = \sqrt{\frac{T_2}{T_1}} \implies 1.5 = \sqrt{\frac{T_2}{273.15}} \implies 2.25 = \frac{T_2}{273.15} \implies T_2 = 2.25 \times 273.15 = 614.59\text{ K}$ (বা $T_2 = 2.25 \times 273 = 614.25\text{ K}$)। সেলসিয়াসে $\theta_2 = 614.25 - 273 = 341.25^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>তাপমাত্রা $T = 614.25\text{ K} = 341.25^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3869,7 +3624,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>খোলা ও বদ্ধ অর্গান পাইপ (সমস্যা 5)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3878,29 +3633,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: খোলা ও বদ্ধ অর্গান পাইপ]
-একটি একমুখ বন্ধ অর্গান নলের দৈর্ঘ্য $L = 120\text{ cm}$। নলটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক এবং ১ম উপসুরের কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+ল্যাপলাসের সংশোধন অনুসারে গ্যাসে শব্দের বেগ $v = \sqrt{\frac{\gamma P}{\rho}}$। স্বাভাবিক তাপমাত্রা ও চাপে (NTP: $P = 1.013 \times 10^5\text{ Pa}$, $\rho = 1.293\text{ kg/m}^3$) বাতাসের জন্য $\gamma = 1.41$ ধরে শব্দের বেগ হিসাব কর এবং নিউটনের সূত্রের মানের সাথে শতকরা ত্রুটি কত ছিল দেখাও।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 5)।</t>
+          <t>ল্যাপলাসের সমীকরণ: $v = \sqrt{\frac{1.41 \times 1.013 \times 10^5}{1.293}} = \sqrt{\frac{142833}{1.293}} = \sqrt{110466.36} \approx 332.38\text{ m/s}$। নিউটনের সমীকরণ অনুযায়ী $v_N = \sqrt{\frac{P}{\rho}} = \sqrt{\frac{1.013 \times 10^5}{1.293}} \approx 279.9\text{ m/s}$। শতকরা পার্থক্য $= \frac{332.38 - 279.9}{332.38} \times 100\% \approx 15.79\%$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>ল্যাপলাসের বেগ $v = 332.38\text{ m/s}$, নিউটনের বেগ $v_{\text{Newton}} = 279.9\text{ m/s}$ (ত্রুটি প্রায় $15.8\%$ কম ছিল)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3920,12 +3675,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>শব্দের তীব্রতা ও ডেসিবেল লেভেল (সমস্যা 6)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3933,25 +3688,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: শব্দের তীব্রতা ও ডেসিবেল লেভেল]
-একটি মাইক হতে নির্গত শব্দের তীব্রতা $I = 2 \times 10^{-5}\text{ W/m}^2$। প্রমাণ তীব্রতা $I_0 = 10^{-12}\text{ W/m}^2$ হলে শব্দের তীব্রতা লেভেল কত ডেসিবেল (dB)?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি শব্দ তরঙ্গের শক্তি ঘনত্ব $u = 2.0 \times 10^{-4}\text{ J/m}^3$ এবং বায়ুতে শব্দের বেগ $340\text{ m/s}$। শব্দটির তীব্রতা $I$ এবং তীব্রতা লেভেল $\beta$ ডেসিবেলে (dB) নির্ণয় কর। ($I_0 = 10^{-12}\text{ W/m}^2$)।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 6)।</t>
+          <t>তীব্রতা ও শক্তি ঘনত্বের সম্পর্ক: $I = u \cdot v = (2.0 \times 10^{-4}\text{ J/m}^3) \times (340\text{ m/s}) = 0.068\text{ W/m}^2$। তীব্রতা লেভেল $\beta = 10\log_{10}\left(\frac{I}{I_0}\right) = 10\log_{10}\left(\frac{0.068}{10^{-12}}\right) = 10\log_{10}(6.8 \times 10^{10}) = 10(10 + \log_{10} 6.8) = 10(10 + 0.8325) = 108.33\text{ dB}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>তীব্রতা $I = 0.068\text{ W/m}^2$, তীব্রতা লেভেল $\beta = 108.33\text{ dB}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3971,7 +3726,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য (সমস্যা 7)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3980,29 +3735,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য]
-বাতাসে শব্দের বেগ $340\text{ m/s}$ এবং কম্পাঙ্ক $400\text{ Hz}$। মাধ্যমের দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 0.5\text{ m}$ হলে তাদের মধ্যকার দশা পার্থক্য কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি শব্দ উৎসের ক্ষমতা $P = 50\text{ W}$। চারদিকে সমভাবে শক্তি বিকিরিত হলে উৎস থেকে $5.0\text{ m}$ এবং $20.0\text{ m}$ দূরত্বে শব্দের তীব্রতা এবং তীব্রতা লেভেলের পার্থক্য $\Delta\beta$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 7)।</t>
+          <t>তীব্রতা $I = \frac{P}{4\pi r^2}$। $r_1 = 5\text{ m}$-এ $I_1 = \frac{50}{4\pi(25)} = \frac{1}{2\pi} \approx 0.15915\text{ W/m}^2$। $r_2 = 20\text{ m}$-এ $I_2 = \frac{50}{4\pi(400)} \approx 0.009947\text{ W/m}^2$। তীব্রতার অনুপাত $\frac{I_1}{I_2} = \left(\frac{r_2}{r_1}\right)^2 = 4^2 = 16$। তীব্রতা লেভেলের পার্থক্য $\Delta\beta = 10\log_{10}(16) = 10(1.2041) \approx 12.04\text{ dB}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$I_1 = 0.159\text{ W/m}^2$, $I_2 = 0.00995\text{ W/m}^2$, পার্থক্য $\Delta\beta = 12.04\text{ dB}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4022,12 +3777,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>অনুরণন নলে প্রান্তীয় ত্রুটি (সমস্যা 8)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4035,25 +3790,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: অনুরণন নলে প্রান্তীয় ত্রুটি]
-একটি অনুনাদ নলে $f = 512\text{ Hz}$ সুরশলাকা দ্বারা প্রথম ও দ্বিতীয় অনুনাদ পাওয়া গেল যথাক্রমে $L_1 = 6.5\text{ cm}$ এবং $L_2 = 7.5\text{ cm}$ পাঠে। শব্দের বেগ ও নলের প্রান্ত ত্রুটি কত?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কারখানার একটি মেশিনের শব্দ তীব্রতা লেভেল $75\text{ dB}$। ওই কারখানায় একই ধরণের আরও $9$টি সমক্ষমতার মেশিন চালু করা হলে মোট তীব্রতা লেভেল কত বৃদ্ধি পাবে এবং মোট লেভেল কত হবে?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 8)।</t>
+          <t>১টি মেশিনের তীব্রতা $I_1$ হলে ১০টি মেশিনের মোট তীব্রতা $I_{\text{total}} = 10 I_1$। মোট লেভেল $\beta_{\text{total}} = 10\log_{10}\left(\frac{10 I_1}{I_0}\right) = 10\log_{10}(10) + 10\log_{10}\left(\frac{I_1}{I_0}\right) = 10 + 75 = 85.0\text{ dB}$। বৃদ্ধি $\Delta\beta = 85 - 75 = 10.0\text{ dB}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>বৃদ্ধি $= 10.0\text{ dB}$, মোট তীব্রতা লেভেল $= 85.0\text{ dB}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4073,7 +3828,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>শব্দের প্রতিফলিত প্রতিধ্বনি (সমস্যা 9)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4082,29 +3837,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: শব্দের প্রতিফলিত প্রতিধ্বনি]
-একজন লোক একটি উঁচু দেয়াল হতে $d = 80\text{ m}$ দূরে দাঁড়িয়ে হাততালি দিল। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে কত সময় পর সে প্রতিধ্বনি শুনতে পাবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার স্থানচ্যুতি $y_1 = 4\sin(500\pi t)$ এবং অপর তরঙ্গের স্থানচ্যুতি $y_2 = 3\sin(500\pi t + \pi/3)$ সেমি। তরঙ্গদ্বয়ের উপরিপাতনে সৃষ্ট লব্ধি তরঙ্গের বিস্তার $A_R$ এবং দশা কোণ $\theta$ কত?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 9)।</t>
+          <t>লব্ধি বিস্তার $A_R = \sqrt{A_1^2 + A_2^2 + 2A_1 A_2 \cos\phi} = \sqrt{4^2 + 3^2 + 2(4)(3)\cos(60^\circ)} = \sqrt{16 + 9 + 24(0.5)} = \sqrt{25 + 12} = \sqrt{37} \approx 6.083\text{ cm}$। দশা কোণ $\tan\theta = \frac{A_2\sin\phi}{A_1 + A_2\cos\phi} = \frac{3\sin 60^\circ}{4 + 3\cos 60^\circ} = \frac{3(\sqrt{3}/2)}{4 + 1.5} = \frac{2.598}{5.5} \approx 0.4724 \implies \theta \approx 25.28^\circ$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>লব্ধি বিস্তার $A_R = 6.08\text{ cm}$, দশা $\theta = 25.28^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4124,12 +3879,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>শব্দের বেগে তাপমাত্রার প্রভাব (সমস্যা 10)</t>
+          <t>অগ্রগামী তরঙ্গ, তীব্রতা ও শক্তি (Progressive Waves, Intensity &amp; Energy)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4137,25 +3892,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: শব্দের বেগে তাপমাত্রার প্রভাব]
-$0^\circ\text{C}$ তাপমাত্রায় বায়ুতে শব্দের বেগ $332\text{ m/s}$ হলে কত তাপমাত্রায় শব্দের বেগ $3100\text{ m/s}$ হবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি তরঙ্গের সমীকরণ $y = 0.02\cos(100\pi t + 5\pi x)$ মিটার। তরঙ্গটির বিস্তার, বেগ এবং গতি অভিমুখ নির্ণয় কর। $x = 0.2\text{ m}$ ও $t = 0.01\text{ s}$ মুহূর্তে কণার সরণ কত?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 10)।</t>
+          <t>সমীকরণ $y = A\cos(\omega t + kx)$ নির্দেশ করে তরঙ্গটি ঋণাত্মক $x$-অক্ষে ধাবমান। বিস্তার $A = 0.02\text{ m}$। কৌণিক বেগ $\omega = 100\pi$, তরঙ্গসংখ্যা $k = 5\pi$। বেগ $v = \frac{\omega}{k} = \frac{100\pi}{5\pi} = 20\text{ m/s}$। $x = 0.2\text{ m}, t = 0.01\text{ s}$-এ দশা $\Phi = 100\pi(0.01) + 5\pi(0.2) = \pi + \pi = 2\pi$। সরণ $y = 0.02\cos(2\pi) = 0.02(1) = 0.02\text{ m}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>বিস্তার $0.02\text{ m}$, বেগ $20\text{ m/s}$ (ঋণাত্মক $x$-অক্ষ বরাবর), সরণ $y = 0.02\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4175,43 +3930,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ (সমস্যা 11)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ]
-##PRESET:wave-transverse[size:medium]##
-একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.012 \sin(200\pi t - 3\pi x)\text{ m}$। তরঙ্গটির বিস্তার, কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের বেগ কত?</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+দুটি বিপরীতমুখী অগ্রগামী তরঙ্গের সমীকরণ $y_1 = 0.06\sin(100\pi t - 2\pi x)$ এবং $y_2 = 0.06\sin(100\pi t + 2\pi x)$ মিটার। এদের উপরিপাতনে গঠিত স্থির তরঙ্গের সমীকরণ, পরপর দুটি নিস্পন্দ বিন্দুর (Nodes) মধ্যবর্তী দূরত্ব এবং $x = 0.125\text{ m}$ বিন্দুতে কণার বিস্তার নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:wave-transverse[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 11)।</t>
+          <t>উপরি পাতন: $y = y_1 + y_2 = 2A\cos(kx)\sin(\omega t) = 2(0.06)\cos(2\pi x)\sin(100\pi t) = 0.12\cos(2\pi x)\sin(100\pi t)$। তরঙ্গসংখ্যা $k = 2\pi \implies \lambda = \frac{2\pi}{k} = 1.0\text{ m}$। পরপর দুটি নিস্পন্দ বিন্দুর দূরত্ব $\frac{\lambda}{2} = 0.5\text{ m}$। $x = 0.125 = \frac{1}{8}\text{ m}$-এ বিস্তার $A' = 0.12\cos(2\pi/8) = 0.12\cos(\pi/4) = 0.12 \times \frac{1}{\sqrt{2}} \approx 0.08485\text{ m}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>স্থির তরঙ্গের সমীকরণ $y = 0.12\cos(2\pi x)\sin(100\pi t)$, নিস্পন্দ বিন্দুর ব্যবধান $0.5\text{ m}$, বিস্তার $0.0849\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4231,7 +3981,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ডপলার ক্রিয়া ও চলমান ট্রেন (সমস্যা 12)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4244,30 +3994,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: ডপলার ক্রিয়া ও চলমান ট্রেন]
-##PRESET:doppler-effect[size:medium]##
-একটি ট্রেনের সাইরেন $f = 200\text{ Hz}$ শব্দ করে $v_s = 50\text{ m/s}$ বেগে প্ল্যাটফর্মের দিকে এগিয়ে আসছে। প্ল্যাটফর্মে দাঁড়ানো একজন শ্রোতার কাছে শব্দের আপাত কম্পাঙ্ক কত মনে হবে? ($v = 340\text{ m/s}$)</t>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি $1.2\text{ m}$ দীর্ঘ তারের উভয় প্রান্ত স্থিরভাবে বাঁধা আছে। তারটিতে $3$টি পূর্ণ লুপ (Three loops / 3rd harmonic) বিশিষ্ট স্থির তরঙ্গ সৃষ্টি হলে এর তরঙ্গদৈর্ঘ্য কত? তরঙ্গের বেগ $240\text{ m/s}$ হলে কম্পাঙ্ক কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:doppler-effect[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 12)।</t>
+          <t>উভয় প্রান্তে আবদ্ধ তারে $n$টি লুপ থাকলে $L = n\frac{\lambda}{2} \implies 1.2 = 3\frac{\lambda}{2} \implies \lambda = \frac{2.4}{3} = 0.80\text{ m}$। কম্পাঙ্ক $f = \frac{v}{\lambda} = \frac{240}{0.80} = 300\text{ Hz}$ (মৌলিক কম্পাঙ্ক $f_1 = \frac{v}{2L} = \frac{240}{2.4} = 100\text{ Hz}$, ৩য় সমমেল $f_3 = 3f_1 = 300\text{ Hz}$)।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>$\lambda = 0.80\text{ m}, f = 300\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4287,38 +4032,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>টান টান তারে স্থির তরঙ্গ (সমস্যা 13)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: টান টান তারে স্থির তরঙ্গ]
-$L = 1.0\text{ m}$ দীর্ঘ এবং $m = 4\text{ g}$ ভরের একটি তারে $T = 700\text{ N}$ টান প্রযুক্ত রয়েছে। তারটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক ($f_1 = \frac{1}{2L}\sqrt{\frac{T}{\mu}}$) কত?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি সোনোমিটারের তারের দৈর্ঘ্য $0.80\text{ m}$ এবং ভর $4.0\text{ g}$। তারটির টান কত হলে এটি $250\text{ Hz}$ কম্পাঙ্কের একটি সুরশলাকার সাথে প্রথম সমমেলে (মৌলিক সুরে) অনুনাদ সৃষ্টি করবে?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 13)।</t>
+          <t>একক দৈর্ঘ্যের ভর $\mu = \frac{m}{L} = \frac{4.0 \times 10^{-3}\text{ kg}}{0.80\text{ m}} = 5.0 \times 10^{-3}\text{ kg/m}$। মৌলিক কম্পাঙ্ক $f = \frac{1}{2L}\sqrt{\frac{T}{\mu}} \implies 250 = \frac{1}{2(0.80)}\sqrt{\frac{T}{5.0\times 10^{-3}}} \implies 250 \times 1.6 = \sqrt{\frac{T}{5\times 10^{-3}}} \implies 400 = \sqrt{\frac{T}{5\times 10^{-3}}}$। বর্গ করে: $160000 = \frac{T}{0.005} \implies T = 160000 \times 0.005 = 800.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>প্রয়োজনীয় টান $T = 800.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4338,7 +4083,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>বিট বা স্বরকম্প গণনা (সমস্যা 14)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4351,25 +4096,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: বিট বা স্বরকম্প গণনা]
-দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে 6টি বিট শোনা যায়। $A$-এর কম্পাঙ্ক $900\text{ Hz}$। $B$-তে কিছুটা মোম লাগালে বিট সংখ্যা বৃদ্ধি পেয়ে 8টি হয়। $B$-এর প্রকৃত কম্পাঙ্ক কত?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1][size:small]##
+একটি তারের টান $44\%$ বৃদ্ধি করা হলে এবং দৈর্ঘ্য $10\%$ হ্রাস করা হলে তারটির মৌলিক কম্পাঙ্ক শতকরা কত বৃদ্ধি পাবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 14)।</t>
+          <t>মৌলিক কম্পাঙ্ক $f = \frac{1}{2L}\sqrt{\frac{T}{\mu}} \propto \frac{\sqrt{T}}{L}$। নতুন টান $T' = 1.44 T \implies \sqrt{T'} = 1.2\sqrt{T}$। নতুন দৈর্ঘ্য $L' = 0.90 L$। নতুন কম্পাঙ্ক $f' = f \left(\frac{\sqrt{1.44}}{0.90}\right) = f \left(\frac{1.20}{0.90}\right) = f \left(\frac{4}{3}\right) = 1.3333 f$। শতকরা বৃদ্ধি $= (1.3333 - 1) \times 100\% = 33.33\%$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>মৌলিক কম্পাঙ্ক বৃদ্ধি পাবে $33.33\%$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4389,38 +4134,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>খোলা ও বদ্ধ অর্গান পাইপ (সমস্যা 15)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: খোলা ও বদ্ধ অর্গান পাইপ]
-একটি একমুখ বন্ধ অর্গান নলের দৈর্ঘ্য $L = 80\text{ cm}$। নলটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক এবং ১ম উপসুরের কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+সোনোমিটারের একটি তারে $T_1 = 16\text{ N}$ টান দিলে এটি $200\text{ Hz}$ কম্পাঙ্কের সুর উৎপন্ন করে। সুরের কম্পাঙ্ক দ্বিগুণ ($400\text{ Hz}$) করতে টান কত গুণ এবং কত নিউটন বৃদ্ধি করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 15)।</t>
+          <t>কম্পাঙ্ক $f \propto \sqrt{T} \implies \frac{f_2}{f_1} = \sqrt{\frac{T_2}{T_1}} \implies 2 = \sqrt{\frac{T_2}{16}} \implies 4 = \frac{T_2}{16} \implies T_2 = 64\text{ N}$। টান বৃদ্ধি করতে হবে $\Delta T = 64 - 16 = 48.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>টান $4$ গুণ অর্থাৎ $64\text{ N}$ করতে হবে (বৃদ্ধি $= 48.0\text{ N}$)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4440,7 +4185,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>শব্দের তীব্রতা ও ডেসিবেল লেভেল (সমস্যা 16)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4453,25 +4198,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: শব্দের তীব্রতা ও ডেসিবেল লেভেল]
-একটি মাইক হতে নির্গত শব্দের তীব্রতা $I = 10 \times 10^{-5}\text{ W/m}^2$। প্রমাণ তীব্রতা $I_0 = 10^{-12}\text{ W/m}^2$ হলে শব্দের তীব্রতা লেভেল কত ডেসিবেল (dB)?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি তারের দুটি অংশের উপরিপাতনে সৃষ্ট স্থির তরঙ্গের পর পর তিনটি নিস্পন্দ বিন্দুর অবস্থান যথাক্রমে $x = 0.15\text{ m}$, $x = 0.35\text{ m}$ এবং $x = 0.55\text{ m}$। মাধ্যমের তরঙ্গবেগ $160\text{ m/s}$ হলে মূল কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 16)।</t>
+          <t>পরপর দুটি নিস্পন্দ বিন্দুর দূরত্ব $\Delta x = \frac{\lambda}{2} = 0.35 - 0.15 = 0.20\text{ m} \implies \lambda = 0.40\text{ m}$। কম্পাঙ্ক $f = \frac{v}{\lambda} = \frac{160}{0.40} = 400.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$\lambda = 0.40\text{ m}, f = 400.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4491,38 +4236,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য (সমস্যা 17)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য]
-বাতাসে শব্দের বেগ $340\text{ m/s}$ এবং কম্পাঙ্ক $1200\text{ Hz}$। মাধ্যমের দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 0.5\text{ m}$ হলে তাদের মধ্যকার দশা পার্থক্য কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1][size:small]##
+একটি তারের উপাদান ইস্পাতের ঘনত্ব $\rho = 7800\text{ kg/m}^3$ এবং তারের ব্যাসার্ধ $r = 0.5\text{ mm}$। তারটিতে $120\text{ N}$ টান দিলে এর মধ্য দিয়ে অনুপ্রস্থ তরঙ্গের বেগ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 17)।</t>
+          <t>প্রস্থচ্ছেদের ক্ষেত্রফল $A = \pi r^2 = \pi (0.5 \times 10^{-3})^2 = 0.25\pi \times 10^{-6}\text{ m}^2 \approx 7.854 \times 10^{-7}\text{ m}^2$। একক দৈর্ঘ্যের ভর $\mu = \rho A = 7800 \times 7.854 \times 10^{-7} \approx 6.126 \times 10^{-3}\text{ kg/m}$। তরঙ্গবেগ $v = \sqrt{\frac{T}{\mu}} = \sqrt{\frac{120}{6.126 \times 10^{-3}}} = \sqrt{19588} \approx 139.96\text{ m/s} \approx 140.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>তরঙ্গবেগ $v = 140.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4542,7 +4287,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>অনুরণন নলে প্রান্তীয় ত্রুটি (সমস্যা 18)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4555,25 +4300,26 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: অনুরণন নলে প্রান্তীয় ত্রুটি]
-একটি অনুনাদ নলে $f = 512\text{ Hz}$ সুরশলাকা দ্বারা প্রথম ও দ্বিতীয় অনুনাদ পাওয়া গেল যথাক্রমে $L_1 = 2.5\text{ cm}$ এবং $L_2 = 7.5\text{ cm}$ পাঠে। শব্দের বেগ ও নলের প্রান্ত ত্রুটি কত?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি স্থির তরঙ্গের সমীকরণ $y = 10\cos\left(rac{\pi x}{15}+ight)\sin(40\pi t)$ সেমি। $x = 0$ হতে প্রথম দুটি সুস্পন্দ বিন্দুর (Antinodes) অবস্থান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 18)।</t>
+          <t>সুস্পন্দ বিন্দুতে বিস্তার সর্বোচ্চ হবে: $\left|\cos\left(\frac{\pi x}{15}\right)\right| = 1 \implies \frac{\pi x}{15} = n\pi \implies x = 15n\text{ cm}$। $n = 0$-এ প্রথম সুস্পন্দ বিন্দু $x_1 = 0\text{ cm}$ এবং $n = 1$-এ দ্বিতীয় সুস্পন্দ বিন্দু $x_2 = 15.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$x_1 = 0\text{ cm}, x_2 = 15.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4593,38 +4339,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>শব্দের প্রতিফলিত প্রতিধ্বনি (সমস্যা 19)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: শব্দের প্রতিফলিত প্রতিধ্বনি]
-একজন লোক একটি উঁচু দেয়াল হতে $d = 40\text{ m}$ দূরে দাঁড়িয়ে হাততালি দিল। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে কত সময় পর সে প্রতিধ্বনি শুনতে পাবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি টানটান তারের দুটি অনুনাদী কম্পাঙ্ক পাওয়া গেল $315\text{ Hz}$ এবং $420\text{ Hz}$। এই দুটি কম্পাঙ্কের মধ্যে অন্য কোনো অনুনাদী কম্পাঙ্ক নেই। তারটির মৌলিক কম্পাঙ্ক এবং এটি কততম হারমোনিকে কম্পিত হচ্ছিল নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 19)।</t>
+          <t>পরপর দুটি হারমোনিকের পার্থক্য মৌলিক কম্পাঙ্কের সমান: $\Delta f = f_{n+1} - f_n = f_1 \implies f_1 = 420 - 315 = 105.0\text{ Hz}$। হারমোনিক সংখ্যা $n = \frac{315}{105} = 3$ এবং $n+1 = \frac{420}{105} = 4$। অতএব ৩য় এবং ৪র্থ হারমোনিক।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>মৌলিক কম্পাঙ্ক $f_1 = 105.0\text{ Hz}$ (৩য় ও ৪র্থ হারমোনিক)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4644,7 +4390,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>শব্দের বেগে তাপমাত্রার প্রভাব (সমস্যা 20)</t>
+          <t>স্থির তরঙ্গ ও সোনোমিটার (Stationary Waves &amp; Sonometer)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4657,25 +4403,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: শব্দের বেগে তাপমাত্রার প্রভাব]
-$0^\circ\text{C}$ তাপমাত্রায় বায়ুতে শব্দের বেগ $332\text{ m/s}$ হলে কত তাপমাত্রায় শব্দের বেগ $360\text{ m/s}$ হবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:rect[w=4.5,h=1][size:small]##
+একটি তারকে নির্দিষ্ট ভারে প্রসারিত রাখা হয়েছে। তারটির দৈর্ঘ্য $50\text{ cm}$ হতে কমিয়ে $40\text{ cm}$ করা হলে কম্পাঙ্কের কী পরিবর্তন হবে এবং শতকরা পরিবর্তন কত?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4.5,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 20)।</t>
+          <t>টান অপরিবর্তিত থাকলে $f \propto \frac{1}{L}$। $\frac{f_2}{f_1} = \frac{L_1}{L_2} = \frac{50}{40} = 1.25$। কম্পাঙ্ক শতকরা বৃদ্ধি $= (1.25 - 1) \times 100\% = 25\%$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>কম্পাঙ্ক $1.25$ গুণ হবে ($25\%$ বৃদ্ধি পাবে)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4695,43 +4441,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ (সমস্যা 21)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ]
-##PRESET:wave-transverse[size:medium]##
-একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.08 \sin(200\pi t - 3\pi x)\text{ m}$। তরঙ্গটির বিস্তার, কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের বেগ কত?</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি দুই মুখ খোলা নলের দৈর্ঘ্য $0.68\text{ m}$ এবং এক মুখ বন্ধ নলের দৈর্ঘ্য $0.85\text{ m}$। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে উভয় নলের মৌলিক কম্পাঙ্ক কত? নলের প্রান্ত সংশোধন অগ্রাহ্য কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:wave-transverse[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 21)।</t>
+          <t>খোলা নলের মৌলিক কম্পাঙ্ক $f_o = \frac{v}{2L_o} = \frac{340}{2(0.68)} = \frac{340}{1.36} = 250.0\text{ Hz}$। বন্ধ নলের মৌলিক কম্পাঙ্ক $f_c = \frac{v}{4L_c} = \frac{340}{4(0.85)} = \frac{340}{3.4} = 100.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>খোলা নলে $f_{\text{open}} = 250.0\text{ Hz}$, বন্ধ নলে $f_{\text{closed}} = 100.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4751,7 +4492,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ডপলার ক্রিয়া ও চলমান ট্রেন (সমস্যা 22)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4764,30 +4505,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: ডপলার ক্রিয়া ও চলমান ট্রেন]
-##PRESET:doppler-effect[size:medium]##
-একটি ট্রেনের সাইরেন $f = 1000\text{ Hz}$ শব্দ করে $v_s = 50\text{ m/s}$ বেগে প্ল্যাটফর্মের দিকে এগিয়ে আসছে। প্ল্যাটফর্মে দাঁড়ানো একজন শ্রোতার কাছে শব্দের আপাত কম্পাঙ্ক কত মনে হবে? ($v = 340\text{ m/s}$)</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি এক মুখ বন্ধ নলে শব্দের বেগ $336\text{ m/s}$। নলটির ব্যাস $d = 4.0\text{ cm}$ এবং প্রকৃত দৈর্ঘ্য $L = 20.0\text{ cm}$। র্যালের প্রান্ত সংশোধন ($e = 0.3d$) বিবেচনা করে নলটির কার্যকর দৈর্ঘ্য এবং বাস্তব মৌলিক কম্পাঙ্ক নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:doppler-effect[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 22)।</t>
+          <t>বন্ধ নলের এক প্রান্তে প্রান্ত সংশোধন $e = 0.3d = 0.3(4.0\text{ cm}) = 1.2\text{ cm}$। কার্যকর দৈর্ঘ্য $L_{\text{eff}} = L + e = 20.0 + 1.2 = 21.2\text{ cm} = 0.212\text{ m}$। মৌলিক কম্পাঙ্ক $f_0 = \frac{v}{4L_{\text{eff}}} = \frac{336}{4(0.212)} = \frac{336}{0.848} \approx 396.23\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>কার্যকর দৈর্ঘ্য $L_{\text{eff}} = 21.2\text{ cm}$, মৌলিক কম্পাঙ্ক $f_0 = 396.23\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4807,38 +4543,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>টান টান তারে স্থির তরঙ্গ (সমস্যা 23)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: টান টান তারে স্থির তরঙ্গ]
-$L = 1.0\text{ m}$ দীর্ঘ এবং $m = 12\text{ g}$ ভরের একটি তারে $T = 700\text{ N}$ টান প্রযুক্ত রয়েছে। তারটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক ($f_1 = \frac{1}{2L}\sqrt{\frac{T}{\mu}}$) কত?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=5][size:small]##
+একটি অনুনাদ নল পরীক্ষায় $512\text{ Hz}$ কম্পাঙ্কের সুরশলাকা দ্বারা প্রথম অনুনাদ পাওয়া গেল $l_1 = 15.8\text{ cm}$ পাঠে এবং দ্বিতীয় অনুনাদ পাওয়া গেল $l_2 = 49.0\text{ cm}$ পাঠে। প্রান্ত সংশোধন $e$ এবং ওই তাপমাত্রায় বায়ুতে শব্দের বেগ $v$ কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 23)।</t>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 2(l_2 - l_1) = 2(49.0 - 15.8) = 2(33.2) = 66.4\text{ cm} = 0.664\text{ m}$। শব্দের বেগ $v = f\lambda = 512 \times 0.664 = 339.968\text{ m/s} \approx 340.0\text{ m/s}$। প্রান্ত সংশোধন $e = \frac{l_2 - 3l_1}{2} = \frac{49.0 - 3(15.8)}{2} = \frac{49.0 - 47.4}{2} = \frac{1.6}{2} = 0.80\text{ cm}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>প্রান্ত সংশোধন $e = 0.80\text{ cm}$, শব্দের বেগ $v = 340.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4858,7 +4594,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>বিট বা স্বরকম্প গণনা (সমস্যা 24)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4871,25 +4607,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: বিট বা স্বরকম্প গণনা]
-দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে 2টি বিট শোনা যায়। $A$-এর কম্পাঙ্ক $900\text{ Hz}$। $B$-তে কিছুটা মোম লাগালে বিট সংখ্যা বৃদ্ধি পেয়ে 6টি হয়। $B$-এর প্রকৃত কম্পাঙ্ক কত?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি খোলা অর্গান নলের তৃতীয় হারমোনিক (3rd harmonic) একটি বন্ধ অর্গান নলের পঞ্চম হারমোনিকের (5th harmonic) সাথে সমান। নল দুটির দৈর্ঘ্যের অনুপাত $L_{	ext{open}} : L_{	ext{closed}}$ কত?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 24)।</t>
+          <t>খোলা নলের $n$-তম হারমোনিক $f_n = n\frac{v}{2L_o}$। ৩য় হারমোনিক $f_{3,o} = \frac{3v}{2L_o}$। বন্ধ নলের বিজোড় হারমোনিক থাকে: ৫ম হারমোনিক ($m = 5$) $f_{5,c} = \frac{5v}{4L_c}$। প্রশ্নমতে $\frac{3v}{2L_o} = \frac{5v}{4L_c} \implies \frac{3}{2L_o} = \frac{5}{4L_c} \implies \frac{L_o}{L_c} = \frac{3 \times 4}{2 \times 5} = \frac{12}{10} = \frac{6}{5} = 1.2$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$L_{\text{open}} : L_{\text{closed}} = 6 : 5 = 1.2$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4909,38 +4645,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>খোলা ও বদ্ধ অর্গান পাইপ (সমস্যা 25)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: খোলা ও বদ্ধ অর্গান পাইপ]
-একটি একমুখ বন্ধ অর্গান নলের দৈর্ঘ্য $L = 40\text{ cm}$। নলটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক এবং ১ম উপসুরের কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি খোলা নলের মৌলিক কম্পাঙ্ক $300\text{ Hz}$। নলটির অর্ধেক পানিতে উল্লম্বভাবে নিমজ্জিত করলে নতুন অবস্থায় এর মৌলিক কম্পাঙ্ক কত হবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 25)।</t>
+          <t>খোলা নলের দৈর্ঘ্য $L$ হলে $f = \frac{v}{2L} = 300\text{ Hz}$। অর্ধেক পানিতে ডুবালে এটি $L/2$ দৈর্ঘ্যের এক মুখ বন্ধ নলে পরিণত হয়। এই বন্ধ নলের মৌলিক কম্পাঙ্ক $f' = \frac{v}{4(L/2)} = \frac{v}{2L} = 300.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>নতুন কম্পাঙ্ক $f' = 300.0\text{ Hz}$ (অপরিবর্তিত থাকবে)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4960,7 +4696,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>শব্দের তীব্রতা ও ডেসিবেল লেভেল (সমস্যা 26)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4973,25 +4709,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: শব্দের তীব্রতা ও ডেসিবেল লেভেল]
-একটি মাইক হতে নির্গত শব্দের তীব্রতা $I = 6 \times 10^{-5}\text{ W/m}^2$। প্রমাণ তীব্রতা $I_0 = 10^{-12}\text{ W/m}^2$ হলে শব্দের তীব্রতা লেভেল কত ডেসিবেল (dB)?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+বায়ুতে শব্দের বেগ $340\text{ m/s}$। একজন ব্যক্তি একটি ফাঁপা নলের মুখে ফুঁ দিয়ে সুর তুলতে চাইলেন। নলটির দৈর্ঘ্য $85\text{ cm}$ এবং উভয় মুখ খোলা। ব্যক্তিটি $2000\text{ Hz}$ পর্যন্ত কম্পাঙ্কের মধ্যে কতটি সুশ্রাব্য হারমোনিক শুনতে পাবেন?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 26)।</t>
+          <t>খোলা নলের মৌলিক কম্পাঙ্ক $f_1 = \frac{v}{2L} = \frac{340}{2(0.85)} = \frac{340}{1.70} = 200\text{ Hz}$। খোলা নলে সকল হারমোনিক ($n f_1$) বিদ্যমান: $f_n = n \times 200\text{ Hz}$। $2000\text{ Hz}$-এর মধ্যে $n = \frac{2000}{200} = 10$। অতএব ১ম হতে ১০ম সমমেল পর্যন্ত মোট ১০টি হারমোনিক শুনতে পাবেন।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>মোট $10$টি হারমোনিক শুনতে পাবেন</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5011,38 +4747,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য (সমস্যা 27)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য]
-বাতাসে শব্দের বেগ $340\text{ m/s}$ এবং কম্পাঙ্ক $800\text{ Hz}$। মাধ্যমের দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 0.5\text{ m}$ হলে তাদের মধ্যকার দশা পার্থক্য কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি একমুখ খোলা নলের ভেতর বাতাস ব্যতীত অন্য একটি গ্যাস পূর্ণ করা হলো যার ঘনত্ব বাতাসের ঘনত্বের $1/4$ অংশ (চাপ অপরিবর্তিত)। নলের মৌলিক কম্পাঙ্ক পূর্বের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 27)।</t>
+          <t>শব্দের বেগ $v \propto \frac{1}{\sqrt{\rho}}$। ঘনত্ব $1/4$ হলে বেগ $v' = 2v$ হবে। কম্পাঙ্ক $f = \frac{v}{4L} \propto v$। সুতরাং নতুন মৌলিক কম্পাঙ্ক পূর্বের দ্বিগুণ হবে।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>কম্পাঙ্ক $2.0$ গুণ হবে ($100\%$ বৃদ্ধি পাবে)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5062,7 +4798,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>অনুরণন নলে প্রান্তীয় ত্রুটি (সমস্যা 28)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5075,25 +4811,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: অনুরণন নলে প্রান্তীয় ত্রুটি]
-একটি অনুনাদ নলে $f = 512\text{ Hz}$ সুরশলাকা দ্বারা প্রথম ও দ্বিতীয় অনুনাদ পাওয়া গেল যথাক্রমে $L_1 = 10.5\text{ cm}$ এবং $L_2 = 7.5\text{ cm}$ পাঠে। শব্দের বেগ ও নলের প্রান্ত ত্রুটি কত?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি সুষম সিলিন্ডারাকার নলের ব্যাস $6.0\text{ cm}$ এবং উভয় মুখ খোলা। প্রান্ত সংশোধন সহ এর কার্যকর দৈর্ঘ্য প্রকৃত দৈর্ঘ্যের চেয়ে কত সেমি বেশি হবে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 28)।</t>
+          <t>উভয় মুখ খোলা নলে দুই প্রান্তেই প্রান্ত সংশোধন যুক্ত হয়: $\Delta L = 2e = 2(0.3d) = 0.6d$। ব্যাস $d = 6.0\text{ cm}$ হলে $\Delta L = 0.6(6.0) = 3.6\text{ cm}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>বৃদ্ধি $\Delta L = 3.6\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5113,38 +4849,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>শব্দের প্রতিফলিত প্রতিধ্বনি (সমস্যা 29)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: শব্দের প্রতিফলিত প্রতিধ্বনি]
-একজন লোক একটি উঁচু দেয়াল হতে $d = 120\text{ m}$ দূরে দাঁড়িয়ে হাততালি দিল। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে কত সময় পর সে প্রতিধ্বনি শুনতে পাবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি বন্ধ অর্গান নলের প্রথম উপসুর (1st overtone) $450\text{ Hz}$। নলটির দ্বিতীয় উপসুর (2nd overtone) এবং মৌলিক কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 29)।</t>
+          <t>বন্ধ নলে কেবল বিজোড় হারমোনিক উৎপন্ন হয়: মৌলিক $f_1$, ১ম উপসুর হলো ৩য় সমমেল $f_1' = 3f_1$, ২য় উপসুর হলো ৫ম সমমেল $f_2' = 5f_1$। $3f_1 = 450 \implies f_1 = 150.0\text{ Hz}$। ২য় উপসুর $= 5f_1 = 5 \times 150 = 750.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>মৌলিক কম্পাঙ্ক $f_1 = 150.0\text{ Hz}$, ২য় উপসুর $f_3 = 750.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5164,7 +4900,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>শব্দের বেগে তাপমাত্রার প্রভাব (সমস্যা 30)</t>
+          <t>অর্গান নল, অনুনাদ নল ও প্রান্ত সংশোধন (Organ Pipes, Resonance &amp; End Correction)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5177,25 +4913,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: শব্দের বেগে তাপমাত্রার প্রভাব]
-$0^\circ\text{C}$ তাপমাত্রায় বায়ুতে শব্দের বেগ $332\text{ m/s}$ হলে কত তাপমাত্রায় শব্দের বেগ $320\text{ m/s}$ হবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি খোলা নলের ২য় হারমোনিক একটি তারের ৩য় হারমোনিকের সাথে একসুরে আছে। তারটির দৈর্ঘ্য $80\text{ cm}$ এবং তারে তরঙ্গের বেগ $120\text{ m/s}$। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে খোলা নলটির দৈর্ঘ্য কত?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 30)।</t>
+          <t>তারের ৩য় হারমোনিক $f_{\text{string}} = 3\left(\frac{v_s}{2L_s}\right) = 3\left(\frac{120}{2 \times 0.80}\right) = 3\left(\frac{120}{1.6}\right) = 3(75) = 225.0\text{ Hz}$। খোলা নলের ২য় হারমোনিক $f_{\text{pipe}} = 2\left(\frac{v_p}{2L_p}\right) = \frac{v_p}{L_p}$। একসুরে থাকায়: $\frac{340}{L_p} = 225 \implies L_p = \frac{340}{225} \approx 1.511\text{ m}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>নলটির দৈর্ঘ্য $L_{\text{pipe}} = 1.511\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5215,43 +4951,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ (সমস্যা 31)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ]
-##PRESET:wave-transverse[size:medium]##
-একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.04 \sin(200\pi t - 3\pi x)\text{ m}$। তরঙ্গটির বিস্তার, কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের বেগ কত?</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে $5$টি বিট শোনা যায়। $A$-এর বাহুতে সামান্য মোম লাগালে বিট সংখ্যা বেড়ে প্রতি সেকেন্ডে $7$টি হয়। সুরশলাকা $B$-এর কম্পাঙ্ক $384\text{ Hz}$ হলে সুরশলাকা $A$-এর মূল কম্পাঙ্ক কত ছিল?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:wave-transverse[size:medium]##</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 31)।</t>
+          <t>বিট সংখ্যা $f_b = |f_A - f_B| = 5 \implies f_A = 384 \pm 5 = 389\text{ Hz}$ অথবা $379\text{ Hz}$। মোম লাগালে ভর বৃদ্ধি পায়, ফলে কম্পাঙ্ক $f_A$ হ্রাস পায় ($f_A' &lt; f_A$)। যদি $f_A = 389$ হতো, তবে তা কমে $384$-এর কাছে আসত, ফলে বিট কমত। কিন্তু বিট বেড়ে $7$ হয়েছে; এর অর্থ $f_A = 379\text{ Hz}$ ছিল, যা কমে $377\text{ Hz}$ হওয়ায় বিট $|377 - 384| = 7$ হয়েছে। অতএব প্রারম্ভিক কম্পাঙ্ক $f_A = 379.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>$f_A = 379.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5271,12 +5002,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ডপলার ক্রিয়া ও চলমান ট্রেন (সমস্যা 32)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5284,30 +5015,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: ডপলার ক্রিয়া ও চলমান ট্রেন]
-##PRESET:doppler-effect[size:medium]##
-একটি ট্রেনের সাইরেন $f = 600\text{ Hz}$ শব্দ করে $v_s = 50\text{ m/s}$ বেগে প্ল্যাটফর্মের দিকে এগিয়ে আসছে। প্ল্যাটফর্মে দাঁড়ানো একজন শ্রোতার কাছে শব্দের আপাত কম্পাঙ্ক কত মনে হবে? ($v = 340\text{ m/s}$)</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+একটি সুরশলাকা $A$-এর কম্পাঙ্ক $256\text{ Hz}$। এটি অন্য একটি সুরশলাকা $B$-এর সাথে একত্রে বাজালে প্রতি সেকেন্ডে $4$টি বিট দেয়। $B$-এর বাহু সামান্য ঘষলে (Filing) বিট সংখ্যা কমে প্রতি সেকেন্ডে $2$টি হয়। সুরশলাকা $B$-এর আদি কম্পাঙ্ক কত ছিল?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:doppler-effect[size:medium]##</t>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 32)।</t>
+          <t>বিট ৪টি হওয়ায় $f_B = 256 \pm 4 = 260\text{ Hz}$ অথবা $252\text{ Hz}$। ঘষলে ভর কমে, ফলে কম্পাঙ্ক বৃদ্ধি পায় ($f_B' &gt; f_B$)। যদি $f_B = 260$ হতো, বৃদ্ধি পেয়ে ব্যবধান বাড়ত ($256$ হতে দূরে যেত)। যেহেতু বিট কমে $2$ হয়েছে, তাই $f_B = 252\text{ Hz}$ ছিল, যা বৃদ্ধি পেয়ে $254\text{ Hz}$ হওয়ায় বিট $|254 - 256| = 2$ হয়েছে। সুতরাং আদি কম্পাঙ্ক $f_B = 252.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>$f_B = 252.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5327,38 +5053,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>টান টান তারে স্থির তরঙ্গ (সমস্যা 33)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: টান টান তারে স্থির তরঙ্গ]
-$L = 1.0\text{ m}$ দীর্ঘ এবং $m = 8\text{ g}$ ভরের একটি তারে $T = 700\text{ N}$ টান প্রযুক্ত রয়েছে। তারটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক ($f_1 = \frac{1}{2L}\sqrt{\frac{T}{\mu}}$) কত?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি সোনোমিটারের তারের দৈর্ঘ্য $100\text{ cm}$ হলে এটি একটি সুরশলাকার সাথে প্রতি সেকেন্ডে $4$টি বিট সৃষ্টি করে। তারটির দৈর্ঘ্য কমিয়ে $95\text{ cm}$ করলে পুনরায় প্রতি সেকেন্ডে $4$টি বিট শোনা যায়। সুরশলাকাটির কম্পাঙ্ক $f$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 33)।</t>
+          <t>দৈর্ঘ্য কমালে তারের কম্পাঙ্ক বৃদ্ধি পায় ($f_w \propto 1/L$)। দৈর্ঘ্য বেশি ($100\text{ cm}$) থাকলে তারের কম্পাঙ্ক সুরশলাকার চেয়ে কম ছিল: $f - f_{100} = 4$। দৈর্ঘ্য কমিয়ে $95\text{ cm}$ করলে তারের কম্পাঙ্ক সুরশলাকাকে অতিক্রম করে বেশি হয়: $f_{95} - f = 4$। অতএব $f_{95} - f_{100} = 8$। আবার $\frac{f_{95}}{f_{100}} = \frac{100}{95} = \frac{20}{19}$। $\frac{20}{19}f_{100} - f_{100} = 8 \implies \frac{1}{19}f_{100} = 8 \implies f_{100} = 152\text{ Hz}$। সুরশলাকার কম্পাঙ্ক $f = 152 + 4 = 156.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$f = 156.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5378,12 +5104,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>বিট বা স্বরকম্প গণনা (সমস্যা 34)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5391,25 +5117,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: বিট বা স্বরকম্প গণনা]
-দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে 10টি বিট শোনা যায়। $A$-এর কম্পাঙ্ক $900\text{ Hz}$। $B$-তে কিছুটা মোম লাগালে বিট সংখ্যা বৃদ্ধি পেয়ে 8টি হয়। $B$-এর প্রকৃত কম্পাঙ্ক কত?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##
+একটি তারের দুটি ভিন্ন টান $T_1 = 100\text{ N}$ এবং $T_2 = 121\text{ N}$-এ একটি নির্দিষ্ট সুরশলাকার সাথে যথাক্রমে $5$টি বিট/সেকেন্ড উৎপন্ন করে। সুরশলাকাটির কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 34)।</t>
+          <t>টান বাড়লে কম্পাঙ্ক বৃদ্ধি পায় ($f \propto \sqrt{T}$)। প্রথম ক্ষেত্রে $f - f_1 = 5$ এবং দ্বিতীয় ক্ষেত্রে $f_2 - f = 5 \implies f_2 - f_1 = 10$। আবার $\frac{f_2}{f_1} = \sqrt{\frac{121}{100}} = \frac{11}{10} = 1.1$। $1.1 f_1 - f_1 = 10 \implies 0.1 f_1 = 10 \implies f_1 = 100\text{ Hz}$। অতএব সুরশলাকার কম্পাঙ্ক $f = 100 + 5 = 105.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$f = 105.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5429,38 +5155,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>খোলা ও বদ্ধ অর্গান পাইপ (সমস্যা 35)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: খোলা ও বদ্ধ অর্গান পাইপ]
-একটি একমুখ বন্ধ অর্গান নলের দৈর্ঘ্য $L = 120\text{ cm}$। নলটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক এবং ১ম উপসুরের কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+দশটি সুরশলাকাকে কম্পাঙ্কের ঊর্ধ্বক্রমে সাজানো হয়েছে যাতে যেকোনো দুটি পাশাপাশি সুরশলাকা একত্রে বাজালে প্রতি সেকেন্ডে $4$টি বিট উৎপন্ন হয়। শেষ সুরশলাকাটির কম্পাঙ্ক যদি প্রথমটির দ্বিগুণ (অক্টেভ) হয়, তবে প্রথম ও শেষ সুরশলাকার কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 35)।</t>
+          <t>$N = 10$টি শলাকা থাকলে মোট ধাপ সংখ্যা $N - 1 = 9$। শেষ শলাকার কম্পাঙ্ক $f_{10} = f_1 + 9 \times 4 = f_1 + 36$। প্রশ্নমতে $f_{10} = 2f_1 \implies 2f_1 = f_1 + 36 \implies f_1 = 36.0\text{ Hz}$। শেষ শলাকা $f_{10} = 2(36) = 72.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>প্রথম শলাকা $f_1 = 36.0\text{ Hz}$, দশম শলাকা $f_{10} = 72.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5480,12 +5206,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>শব্দের তীব্রতা ও ডেসিবেল লেভেল (সমস্যা 36)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5493,25 +5219,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: শব্দের তীব্রতা ও ডেসিবেল লেভেল]
-একটি মাইক হতে নির্গত শব্দের তীব্রতা $I = 2 \times 10^{-5}\text{ W/m}^2$। প্রমাণ তীব্রতা $I_0 = 10^{-12}\text{ W/m}^2$ হলে শব্দের তীব্রতা লেভেল কত ডেসিবেল (dB)?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি শব্দ তরঙ্গের সমীকরণ $y_1 = 4\sin(604\pi t)$ এবং $y_2 = 4\sin(600\pi t)$ মিটার। এদের উপরিপাতনে সৃষ্ট প্রতি সেকেন্ডে বিট সংখ্যা কত এবং তীব্রতার পর্যায়কাল কত?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 36)।</t>
+          <t>কম্পাঙ্ক $f_1 = \frac{604\pi}{2\pi} = 302\text{ Hz}$ এবং $f_2 = \frac{600\pi}{2\pi} = 300\text{ Hz}$। বিট সংখ্যা $f_b = |f_1 - f_2| = 302 - 300 = 2\text{ s}^{-1}$। বিটের পর্যায়কাল $T_b = \frac{1}{f_b} = \frac{1}{2} = 0.50\text{ s}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>বিট সংখ্যা $2\text{ s}^{-1}$, বিট পর্যায়কাল $T_b = 0.50\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5531,38 +5257,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য (সমস্যা 37)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য]
-বাতাসে শব্দের বেগ $340\text{ m/s}$ এবং কম্পাঙ্ক $400\text{ Hz}$। মাধ্যমের দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 0.5\text{ m}$ হলে তাদের মধ্যকার দশা পার্থক্য কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=4][size:small]##
+একটি সুরশলাকা $A$ অপর একটি শলাকা $B$ ($f_B = 300\text{ Hz}$)-এর সাথে বাজালে $6\text{ বিট/সেকেন্ড}$ উৎপন্ন করে। শলাকা $A$-কে কিছুটা ক্ষয় করলে বিট সংখ্যা অপরিবর্তিত থাকে ($6\text{ বিট/সেকেন্ড}$)। শলাকা $A$-এর প্রারম্ভিক ও অন্তিম কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 37)।</t>
+          <t>ক্ষয় করলে কম্পাঙ্ক বৃদ্ধি পায় ($f_A' &gt; f_A$)। যদি আদি কম্পাঙ্ক $f_B$-এর নিচে থাকে ($f_A = 300 - 6 = 294\text{ Hz}$), তা বৃদ্ধি পেয়ে $300$-কে অতিক্রম করে ঠিক ততটুকুই উপরে ($f_A' = 300 + 6 = 306\text{ Hz}$) পৌঁছালে উভয় অবস্থাতেই বিট সংখ্যা $6$ হতে পারে। সুতরাং আদি কম্পাঙ্ক $294.0\text{ Hz}$ এবং ঘষার পর $306.0\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>প্রারম্ভিক $f_A = 294.0\text{ Hz}$, অন্তিম $f_A' = 306.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5582,12 +5308,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>অনুরণন নলে প্রান্তীয় ত্রুটি (সমস্যা 38)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5595,25 +5321,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: অনুরণন নলে প্রান্তীয় ত্রুটি]
-একটি অনুনাদ নলে $f = 512\text{ Hz}$ সুরশলাকা দ্বারা প্রথম ও দ্বিতীয় অনুনাদ পাওয়া গেল যথাক্রমে $L_1 = 6.5\text{ cm}$ এবং $L_2 = 7.5\text{ cm}$ পাঠে। শব্দের বেগ ও নলের প্রান্ত ত্রুটি কত?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি বাদ্যযন্ত্র হতে নির্গত সুরের তরঙ্গদৈর্ঘ্য যথাক্রমে $\lambda_1 = 1.00\text{ m}$ এবং $\lambda_2 = 1.02\text{ m}$। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে যন্ত্র দুটি একত্রে বাজালে প্রতি সেকেন্ডে কয়টি বিট শোনা যাবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 38)।</t>
+          <t>কম্পাঙ্ক $f_1 = \frac{v}{\lambda_1} = \frac{340}{1.00} = 340.0\text{ Hz}$। $f_2 = \frac{v}{\lambda_2} = \frac{340}{1.02} \approx 333.33\text{ Hz}$। বিট সংখ্যা $f_b = |f_1 - f_2| = 340 - 333.33 = 6.67\text{ s}^{-1}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>বিট সংখ্যা $6.67\text{ s}^{-1} \approx 7\text{ টি/সেকেন্ড}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5633,38 +5359,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>শব্দের প্রতিফলিত প্রতিধ্বনি (সমস্যা 39)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: শব্দের প্রতিফলিত প্রতিধ্বনি]
-একজন লোক একটি উঁচু দেয়াল হতে $d = 80\text{ m}$ দূরে দাঁড়িয়ে হাততালি দিল। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে কত সময় পর সে প্রতিধ্বনি শুনতে পাবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=1][size:small]##
+একটি তারে টান $2\%$ বৃদ্ধি পেলে একটি সুরশলাকার সাথে উৎপন্ন বিট সংখ্যা $4\text{ s}^{-1}$ হতে হ্রাস পেয়ে শূন্য হয়ে যায়। সুরশলাকাটির কম্পাঙ্ক কত ছিল?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=1][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 39)।</t>
+          <t>টান বাড়লে তারের কম্পাঙ্ক বাড়ে। পূর্বে বিট $4$ ছিল এবং টান বাড়ালে তা কমে শূন্য হয়; অর্থাৎ তারের আদি কম্পাঙ্ক সুরশলাকার চেয়ে $4\text{ Hz}$ কম ছিল: $f_s - f_w = 4$। ক্ষুদ্র পরিবর্তনে $\frac{\Delta f_w}{f_w} \approx \frac{1}{2}\frac{\Delta T}{T} = \frac{1}{2}(0.02) = 0.01$। কম্পাঙ্ক বৃদ্ধি $\Delta f_w = 0.01 f_w = 4 \implies f_w = 400\text{ Hz}$। সুরশলাকার কম্পাঙ্ক $f_s = 400 + 4$ বা আনুপাতিক হারে $f_s = 404\text{ Hz}$ (অথবা নিখুঁতভাবে $f_s = 400\text{ Hz}$ যদি আদি মান ধরা হয়)।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>সুরশলাকার কম্পাঙ্ক $f = 400.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5684,12 +5410,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>শব্দের বেগে তাপমাত্রার প্রভাব (সমস্যা 40)</t>
+          <t>বীট ও সুরশলাকার কম্পন (Beats &amp; Tuning Forks)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5697,25 +5423,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: শব্দের বেগে তাপমাত্রার প্রভাব]
-$0^\circ\text{C}$ তাপমাত্রায় বায়ুতে শব্দের বেগ $332\text{ m/s}$ হলে কত তাপমাত্রায় শব্দের বেগ $3100\text{ m/s}$ হবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি অর্গান নলে তাপমাত্রা $15^\circ\text{C}$ হতে বৃদ্ধি পেয়ে $25^\circ\text{C}$ হলো। এতে একটি নির্দিষ্ট শলাকার সাথে প্রতি সেকেন্ডে $3$টি বিট শোনা গেল। $15^\circ\text{C}$-এ কোনো বিট শোনা না গেলে শলাকাটির কম্পাঙ্ক কত ছিল?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 40)।</t>
+          <t>নলের কম্পাঙ্ক $f_T \propto v \propto \sqrt{T}$। $\frac{f_{25}}{f_{15}} = \sqrt{\frac{273+25}{273+15}} = \sqrt{\frac{298}{288}} = \sqrt{1.03472} \approx 1.0172$। বিট সংখ্যা $\Delta f = f_{25} - f_{15} = 0.0172 f_{15} = 3 \implies f_{15} = \frac{3}{0.0172} \approx 174.4\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>শলাকার কম্পাঙ্ক $f \approx 173.0\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5735,43 +5461,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ (সমস্যা 41)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: অগ্রগামী তরঙ্গের সমীকরণ বিশ্লেষণ]
-##PRESET:wave-transverse[size:medium]##
-একটি অগ্রগামী তরঙ্গের সমীকরণ $y = 0.012 \sin(200\pi t - 3\pi x)\text{ m}$। তরঙ্গটির বিস্তার, কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের বেগ কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি ট্রেন $v_s = 72\text{ km/h}$ বেগে বাঁশি বাজাতে বাজাতে স্টেশনে দাঁড়ানো একজন শ্রোতার দিকে এগিয়ে আসছে। বাঁশির প্রকৃত কম্পাঙ্ক $600\text{ Hz}$ এবং বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে (ক) ট্রেনটি কাছে আসার সময় এবং (খ) স্টেশন অতিক্রম করে দূরে চলে যাওয়ার সময় শ্রোতার অনুভূত আপাত কম্পাঙ্ক কত হবে?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:wave-transverse[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 41)।</t>
+          <t>উৎস বেগ $v_s = \frac{72 \times 1000}{3600} = 20\text{ m/s}$। শ্রোতা স্থির ($v_o = 0$)। (ক) কাছে আসার সময়: $f' = f\left(\frac{v}{v - v_s}\right) = 600\left(\frac{340}{340 - 20}\right) = 600\left(\frac{340}{320}\right) = 600 \times 1.0625 = 637.5\text{ Hz}$। (খ) দূরে যাওয়ার সময়: $f'' = f\left(\frac{v}{v + v_s}\right) = 600\left(\frac{340}{340 + 20}\right) = 600\left(\frac{340}{360}\right) = \frac{600 \times 17}{18} \approx 566.67\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(ক) কাছে আসার সময় $f' = 637.5\text{ Hz}$, (খ) দূরে যাওয়ার সময় $f'' = 566.67\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5791,12 +5512,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ডপলার ক্রিয়া ও চলমান ট্রেন (সমস্যা 42)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5804,30 +5525,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: ডপলার ক্রিয়া ও চলমান ট্রেন]
-##PRESET:doppler-effect[size:medium]##
-একটি ট্রেনের সাইরেন $f = 200\text{ Hz}$ শব্দ করে $v_s = 50\text{ m/s}$ বেগে প্ল্যাটফর্মের দিকে এগিয়ে আসছে। প্ল্যাটফর্মে দাঁড়ানো একজন শ্রোতার কাছে শব্দের আপাত কম্পাঙ্ক কত মনে হবে? ($v = 340\text{ m/s}$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি স্থির শব্দ উৎসের দিকে একটি গাড়ি $v_o = 34\text{ m/s}$ বেগে ধাবিত হচ্ছে। শব্দের বেগ $340\text{ m/s}$ হলে আপাত কম্পাঙ্ক প্রকৃত কম্পাঙ্কের শতকরা কত বৃদ্ধি পাবে?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:doppler-effect[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 42)।</t>
+          <t>উৎস স্থির ($v_s = 0$) এবং শ্রোতা উৎসের দিকে গতিশীল ($v_o = 34\text{ m/s}$)। আপাত কম্পাঙ্ক $f' = f\left(\frac{v + v_o}{v}\right) = f\left(\frac{340 + 34}{340}\right) = f\left(\frac{374}{340}\right) = 1.10 f$। শতকরা বৃদ্ধি $= (1.10 - 1) \times 100\% = 10.0\%$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>আপাত কম্পাঙ্ক $10.0\%$ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5847,38 +5563,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>টান টান তারে স্থির তরঙ্গ (সমস্যা 43)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: টান টান তারে স্থির তরঙ্গ]
-$L = 1.0\text{ m}$ দীর্ঘ এবং $m = 4\text{ g}$ ভরের একটি তারে $T = 700\text{ N}$ টান প্রযুক্ত রয়েছে। তারটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক ($f_1 = \frac{1}{2L}\sqrt{\frac{T}{\mu}}$) কত?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=1,h=4][size:small]##
+একটি গাড়ির সাইরেনের কম্পাঙ্ক $800\text{ Hz}$। গাড়িটি $v = 20\text{ m/s}$ দ্রুতিতে একটি উল্লম্ব খাড়া দেওয়ালের দিকে এগিয়ে যাচ্ছে। দেওয়াল থেকে প্রতিফলিত প্রতিধ্বনি গাড়ির চালক কত কম্পাঙ্কে শুনতে পাবেন? ($v_{	ext{sound}} = 340\text{ m/s}$)। চালক প্রতি সেকেন্ডে কয়টি বিট শুনতে পাবেন?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=1,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 43)।</t>
+          <t>দেওয়ালের আপাত আপতিত কম্পাঙ্ক $f' = f\left(\frac{v}{v - u}\right) = 800\left(\frac{340}{340 - 20}\right) = 800\left(\frac{340}{320}\right) = 850\text{ Hz}$। প্রতিফলনের পর দেওয়াল স্থির উৎস এবং চালক দেওয়ালের দিকে গতিশীল শ্রোতা: চালকের অনুভূত কম্পাঙ্ক $f'' = f'\left(\frac{v + u}{v}\right) = 850\left(\frac{340 + 20}{340}\right) = 850\left(\frac{360}{340}\right) = 900.0\text{ Hz}$। চালকের কাছে সরাসরি শব্দ $800\text{ Hz}$, ফলে বিট $= 900 - 800 = 100\text{ s}^{-1}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>প্রতিধ্বনির কম্পাঙ্ক $f'' = 900.0\text{ Hz}$, বিট সংখ্যা $= 100\text{ s}^{-1}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5898,12 +5614,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>বিট বা স্বরকম্প গণনা (সমস্যা 44)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5911,25 +5627,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: বিট বা স্বরকম্প গণনা]
-দুটি সুরশলাকা $A$ ও $B$ একত্রে বাজালে প্রতি সেকেন্ডে 6টি বিট শোনা যায়। $A$-এর কম্পাঙ্ক $900\text{ Hz}$। $B$-তে কিছুটা মোম লাগালে বিট সংখ্যা বৃদ্ধি পেয়ে 6টি হয়। $B$-এর প্রকৃত কম্পাঙ্ক কত?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+দুটি ট্রেন একই লাইনে পরস্পরের বিপরীত দিকে যথাক্রমে $54\text{ km/h}$ এবং $72\text{ km/h}$ বেগে ধাবিত হচ্ছে। ১ম ট্রেনের হুইসেলের কম্পাঙ্ক $500\text{ Hz}$ হলে ২য় ট্রেনের ড্রাইভার কর্তৃক অনুভূত কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 44)।</t>
+          <t>১ম ট্রেনের বেগ (উৎস) $v_s = \frac{54 \times 1000}{3600} = 15\text{ m/s}$। ২য় ট্রেনের বেগ (শ্রোতা) $v_o = \frac{72 \times 1000}{3600} = 20\text{ m/s}$। উভয়ে পরস্পরের দিকে অগ্রসরমান হওয়ায়: $f' = f\left(\frac{v + v_o}{v - v_s}\right) = 500\left(\frac{340 + 20}{340 - 15}\right) = 500\left(\frac{360}{325}\right) = 500 \times 1.1077 \approx 553.85\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>আপাত কম্পাঙ্ক $f' = 553.85\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5949,38 +5665,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>খোলা ও বদ্ধ অর্গান পাইপ (সমস্যা 45)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: খোলা ও বদ্ধ অর্গান পাইপ]
-একটি একমুখ বন্ধ অর্গান নলের দৈর্ঘ্য $L = 80\text{ cm}$। নলটিতে উৎপন্ন মূল সুরের কম্পাঙ্ক এবং ১ম উপসুরের কম্পাঙ্ক কত? ($v = 340\text{ m/s}$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বায়ু প্রবাহের প্রভাব: একটি স্থির সুরশলাকা হতে $400\text{ Hz}$ কম্পাঙ্কের শব্দ নির্গত হচ্ছে। উৎস হতে শ্রোতার দিকে $v_w = 20\text{ m/s}$ বেগে বায়ু প্রবাহিত হচ্ছে। শ্রোতা স্থির থাকলে আপাত কম্পাঙ্ক এবং তরঙ্গদৈর্ঘ্যের কী পরিবর্তন হবে? ($v = 340\text{ m/s}$)।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 45)।</t>
+          <t>উৎস ও শ্রোতা উভয়ই স্থির থাকলে মাধ্যম গতিশীল হলেও প্রতি সেকেন্ডে শ্রোতার কাছে পৌঁছানো তরঙ্গের সংখ্যা পরিবর্তিত হয় না, ফলে আপাত কম্পাঙ্ক $f' = f = 400.0\text{ Hz}$ অপরিবর্তিত থাকে। কিন্তু শব্দের কার্যকর বেগ বৃদ্ধি পেয়ে $v' = v + v_w = 340 + 20 = 360\text{ m/s}$ হয়। ফলে তরঙ্গদৈর্ঘ্য বৃদ্ধি পায়: $\lambda' = \frac{v'}{f} = \frac{360}{400} = 0.90\text{ m}$ (স্থির অবস্থায় ছিল $\frac{340}{400} = 0.85\text{ m}$)।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>আপাত কম্পাঙ্ক অপরিবর্তিত ($400.0\text{ Hz}$), তরঙ্গদৈর্ঘ্য বেড়ে $\lambda' = 0.90\text{ m}$ হবে</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6000,12 +5716,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>শব্দের তীব্রতা ও ডেসিবেল লেভেল (সমস্যা 46)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6013,25 +5729,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: শব্দের তীব্রতা ও ডেসিবেল লেভেল]
-একটি মাইক হতে নির্গত শব্দের তীব্রতা $I = 10 \times 10^{-5}\text{ W/m}^2$। প্রমাণ তীব্রতা $I_0 = 10^{-12}\text{ W/m}^2$ হলে শব্দের তীব্রতা লেভেল কত ডেসিবেল (dB)?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পুলিশ ভ্যান $v_s$ বেগে একটি সাইরেন বাজিয়ে স্থির পথচারীর দিকে এগিয়ে এসে তাকে অতিক্রম করে চলে গেল। পথচারী লক্ষ্য করলেন অতিক্রম করার পর কম্পাঙ্কের শতকরা পরিবর্তন হলো $10\%$। শব্দের বেগ $340\text{ m/s}$ হলে ভ্যানের বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 46)।</t>
+          <t>আসার সময় $f_1 = f\frac{v}{v - v_s}$ এবং যাওয়ার সময় $f_2 = f\frac{v}{v + v_s}$। অনুপাত $\frac{f_2}{f_1} = \frac{v - v_s}{v + v_s} = 0.90 \implies v - v_s = 0.90(v + v_s) \implies 0.10 v = 1.90 v_s \implies v_s = \frac{0.10}{1.90} v = \frac{340}{19} \approx 17.89\text{ m/s}$ (যদি হ্রাসের শতকরা হার $10\%$ হয়)।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>ভ্যানের বেগ $v_s = 17.44\text{ m/s} \approx 62.8\text{ km/h}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6051,38 +5767,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য (সমস্যা 47)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: তরঙ্গের পথ পার্থক্য ও দশা পার্থক্য]
-বাতাসে শব্দের বেগ $340\text{ m/s}$ এবং কম্পাঙ্ক $1200\text{ Hz}$। মাধ্যমের দুটি বিন্দুর মধ্যে পথ পার্থক্য $\Delta x = 0.5\text{ m}$ হলে তাদের মধ্যকার দশা পার্থক্য কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বাদুড় $v = 10\text{ m/s}$ বেগে উড়ে যাওয়ার সময় $40\text{ kHz}$ কম্পাঙ্কের আল্ট্রাসাউন্ড তরঙ্গ নির্গত করল। সামনে একটি স্থির পতঙ্গ থেকে প্রতিফলিত প্রতিধ্বনি বাদুড়টি কত কম্পাঙ্কে শুনতে পাবে? ($v_{	ext{sound}} = 340\text{ m/s}$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 47)।</t>
+          <t>পতঙ্গে আপতিত কম্পাঙ্ক $f' = f\left(\frac{v}{v - u}\right) = 40\left(\frac{340}{340 - 10}\right) = 40\left(\frac{340}{330}\right)$। প্রতিফলিত তরঙ্গ বাদুড়ে পৌঁছানোর সময় বাদুড় শ্রোতা হিসেবে পতঙ্গের দিকে ধাবমান: $f'' = f'\left(\frac{v + u}{v}\right) = 40\left(\frac{340}{330}\right)\left(\frac{350}{340}\right) = 40\left(\frac{350}{330}\right) = 40(1.0606) \approx 42.42\text{ kHz}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>প্রতিধ্বনির কম্পাঙ্ক $f'' = 42.42\text{ kHz}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6102,12 +5818,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>অনুরণন নলে প্রান্তীয় ত্রুটি (সমস্যা 48)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6115,25 +5831,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: অনুরণন নলে প্রান্তীয় ত্রুটি]
-একটি অনুনাদ নলে $f = 512\text{ Hz}$ সুরশলাকা দ্বারা প্রথম ও দ্বিতীয় অনুনাদ পাওয়া গেল যথাক্রমে $L_1 = 2.5\text{ cm}$ এবং $L_2 = 7.5\text{ cm}$ পাঠে। শব্দের বেগ ও নলের প্রান্ত ত্রুটি কত?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সাবমেরিন $A$ $18\text{ km/h}$ বেগে অপর একটি সাবমেরিন $B$ ($12\text{ km/h}$ বেগে দূরে সরে যাচ্ছে)-কে তাড়া করছে। সাবমেরিন $A$ হতে নির্গত সোনার সিগন্যালের কম্পাঙ্ক $1000\text{ Hz}$ এবং পানিতে শব্দের বেগ $1500\text{ m/s}$ হলে সাবমেরিন $B$ কত কম্পাঙ্কের সিগন্যাল গ্রহণ করবে?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 48)।</t>
+          <t>$v_s = \frac{18 \times 1000}{3600} = 5.0\text{ m/s}$ (ধাবমান), $v_o = \frac{12 \times 1000}{3600} = 3.33\text{ m/s}$ (দূরে সরে যাচ্ছে)। আপাত কম্পাঙ্ক $f' = f\left(\frac{v - v_o}{v - v_s}\right) = 1000\left(\frac{1500 - 3.33}{1500 - 5.0}\right) = 1000\left(\frac{1496.67}{1495.0}\right) \approx 1001.12\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>গৃহীত কম্পাঙ্ক $f' = 1001.1\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6153,38 +5869,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>শব্দের প্রতিফলিত প্রতিধ্বনি (সমস্যা 49)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: শব্দের প্রতিফলিত প্রতিধ্বনি]
-একজন লোক একটি উঁচু দেয়াল হতে $d = 40\text{ m}$ দূরে দাঁড়িয়ে হাততালি দিল। বায়ুতে শব্দের বেগ $340\text{ m/s}$ হলে কত সময় পর সে প্রতিধ্বনি শুনতে পাবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##
+একটি জেট বিমান শব্দের বেগের দ্বিগুণ বেগে ($M = 2$, Mach 2) অনুভূমিকভাবে আকাশে উড়ে যাচ্ছে। সৃষ্ট শক ওয়েভের (Shock wave) শঙ্কু কোণ (Mach angle $lpha$) কত ডিগ্রি হবে?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 49)।</t>
+          <t>ম্যাক কোণ $\sin\alpha = \frac{v_{\text{sound}}}{v_{\text{source}}} = \frac{1}{M}$। $M = 2$ হলে $\sin\alpha = \frac{1}{2} \implies \alpha = \arcsin(0.5) = 30.0^\circ$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>ম্যাক কোণ $\alpha = 30.0^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6204,12 +5920,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>শব্দের বেগে তাপমাত্রার প্রভাব (সমস্যা 50)</t>
+          <t>ডপলার ক্রিয়া ও বিশেষ তরঙ্গ বিষয়াবলী (Doppler Effect &amp; Shock Waves)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6217,25 +5933,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: শব্দের বেগে তাপমাত্রার প্রভাব]
-$0^\circ\text{C}$ তাপমাত্রায় বায়ুতে শব্দের বেগ $332\text{ m/s}$ হলে কত তাপমাত্রায় শব্দের বেগ $360\text{ m/s}$ হবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সাইরেন একটি অনুভূমিক বৃত্তাকার পথে $R = 1.0\text{ m}$ ব্যাসার্ধে $\omega = 20\text{ rad/s}$ কৌণিক বেগে ঘুরছে। সাইরেনের কম্পাঙ্ক $500\text{ Hz}$ এবং শব্দের বেগ $340\text{ m/s}$। বৃত্তের বাইরে দূরবর্তী কোনো স্থির পর্যবেক্ষক কর্তৃক অনুভূত সর্বোচ্চ এবং সর্বনিম্ন আপাত কম্পাঙ্ক কত?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>অগ্রগামী ও স্থির তরঙ্গের সূত্রাবলি এবং ডপলার ক্রিয়ার সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 50)।</t>
+          <t>রৈখিক বেগ $u = \omega R = 20 \times 1.0 = 20\text{ m/s}$। সর্বোচ্চ কম্পাঙ্ক যখন সাইরেন পর্যবেক্ষকের দিকে গতিশীল: $f_{\max} = f\frac{v}{v - u} = 500\left(\frac{340}{340 - 20}\right) = 500\left(\frac{340}{320}\right) = 531.25\text{ Hz}$। সর্বনিম্ন কম্পাঙ্ক যখন সাইরেন পর্যবেক্ষক হতে দূরে সরে যায়: $f_{\min} = f\frac{v}{v + u} = 500\left(\frac{340}{340 + 20}\right) = 500\left(\frac{340}{360}\right) \approx 472.22\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>তরঙ্গ তত্ত্বের উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>সর্বোচ্চ $f_{\max} = 531.25\text{ Hz}$, সর্বনিম্ন $f_{\min} = 472.22\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
